--- a/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
+++ b/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Audit" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Katalog!$A$1:$Y$285</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Katalog!$A$1:$Y$292</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Mundarija!$A$1:$I$254</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Qidiruv navbati'!$A$1:$F$117</definedName>
   </definedNames>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6690" uniqueCount="2355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6809" uniqueCount="2379">
   <si>
     <t xml:space="preserve">SHOKALON — videodarslar katalogi, 7-versiya</t>
   </si>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Nima bor</t>
   </si>
   <si>
-    <t xml:space="preserve">33 bob, 253 kichik mavzu (Mundarija); 284 ta video (Katalog) — ilovadagi barcha darslar shu yerda kod va Video ID bilan; rad etilgan havolalar; bob bo‘yicha qamrov; audit va loyihadan chetga chiqishlar.</t>
+    <t xml:space="preserve">33 bob, 253 kichik mavzu (Mundarija); 291 ta video (Katalog) — ilovadagi barcha darslar shu yerda kod va Video ID bilan; rad etilgan havolalar; bob bo‘yicha qamrov; audit va loyihadan chetga chiqishlar.</t>
   </si>
   <si>
     <t xml:space="preserve">Mavzu kodi</t>
@@ -6175,6 +6175,15 @@
     <t xml:space="preserve">V269</t>
   </si>
   <si>
+    <t xml:space="preserve">Monophasic, Biphasic &amp; Triphasic Spectral Doppler Waveforms | Vascular Ultrasound Analysis (USG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=IaejYqKM6mI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V270</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vascular Imaging Webinar Series: Physics, Knobology, And Hemodynamics</t>
   </si>
   <si>
@@ -6184,21 +6193,195 @@
     <t xml:space="preserve">PAHO TV</t>
   </si>
   <si>
-    <t xml:space="preserve">Xalqaro tashkilot (PAHO / JSST mintaqaviy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monophasic, Biphasic &amp; Triphasic Spectral Doppler Waveforms | Vascular Ultrasound Analysis (USG)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=IaejYqKM6mI</t>
+    <t xml:space="preserve">Xalqaro sog‘liqni saqlash tashkiloti (PAHO/WHO) vebinari; tili tekshirilmagan (nomi inglizcha)</t>
   </si>
   <si>
     <t xml:space="preserve">V271</t>
   </si>
   <si>
+    <t xml:space="preserve">Hot Tips - Finding the Vertebral Artery with Ultrasound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=_CAkI846j7E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete Subclavian Artery Steal Syndrome  ultrasound criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=dRVXK3DjBzk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radcliffe Cardiology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ta’lim kanali (Radcliffe Cardiology)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAC Carotid Stenosis Diagnostic Criteria: A Discussion with Dr. Heather Gornik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=pXjCmheNuug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intersocietal Accreditation Commission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akkreditatsiya tashkiloti (IAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severe stenosis of the internal carotid artery: ultrasound diagnostic criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=76hyW1-XkGk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to Perform and Interpret Peripheral Arterial Doppler Examinations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=4JyRA2xSQ6o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upper Extremity Arterial Duplex Anatomy and Protocol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=J4z7BCopSvs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpreting duplex waveforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=Vf7nE0vBSco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part 1: Varicose veins ultrasound assessment: GSV anatomy assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=n5HblR27soE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part 3: Primary varicose veins of the great saphenous vein. Saphenofemoral junction reflux test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=QFDDU7lpsuA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vascular Imaging Webinar Series: DVT And Venous Insufficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=KLt-sO1G74A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abdominal Aortic Aneurysm (AAA): Ultrasound Scanning Technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=IbSW2GCMsoQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Point of Care Ultrasound of the Abdominal Aorta - AMBOSS Video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=w8wc8-40F1E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMBOSS: Medical Knowledge Distilled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ta’lim platformasi (AMBOSS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Point of Care Ultrasound of the Inferior Vena Cava (IVC) - AMBOSS Video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=Flc8xS2foOU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultrasound Vessel Mapping for Dialysis Access Planning (Eric Peden, MD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=EjXcrvJTmYw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kasalxona (Houston Methodist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vascular Imaging Webinar Series: Arteriovenous Mapping for Dialysis Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=cFHfoL1k_pk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to Scan Dialysis Fistulas -Ultrasound Tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=-8VG1bBhchI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renal/Kidney Transplant Duplex Protocol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=KGFphcefwXA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultrasound of Renal Transplant Vascular Complications: What to Know</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=eNsLjk2fJxc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V289</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vertebral Arteries &amp; Subclavian Steal: Here's the Breakdown You Need by an Ultrasound Tech</t>
   </si>
   <si>
@@ -6208,127 +6391,7 @@
     <t xml:space="preserve">Path2Passing </t>
   </si>
   <si>
-    <t xml:space="preserve">V272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete Subclavian Artery Steal Syndrome  ultrasound criteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=dRVXK3DjBzk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radcliffe Cardiology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ta’lim kanali (Radcliffe Cardiology)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAC Carotid Stenosis Diagnostic Criteria: A Discussion with Dr. Heather Gornik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=pXjCmheNuug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intersocietal Accreditation Commission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akkreditatsiya tashkiloti (IAC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severe stenosis of the internal carotid artery: ultrasound diagnostic criteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=76hyW1-XkGk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part 1: Varicose veins ultrasound assessment: GSV anatomy assessment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=n5HblR27soE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part 3: Primary varicose veins of the great saphenous vein. Saphenofemoral junction reflux test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=QFDDU7lpsuA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vascular Imaging Webinar Series: DVT And Venous Insufficiency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=KLt-sO1G74A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Point of Care Ultrasound of the Abdominal Aorta - AMBOSS Video</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=w8wc8-40F1E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMBOSS: Medical Knowledge Distilled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ta’lim platformasi (AMBOSS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03.15.02; 11.29.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Point of Care Ultrasound of the Inferior Vena Cava (IVC) - AMBOSS Video</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=Flc8xS2foOU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abdominal Aortic Aneurysm (AAA): Ultrasound Scanning Technique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=IbSW2GCMsoQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultrasound of Renal Transplant Vascular Complications: What to Know</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=eNsLjk2fJxc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renal/Kidney Transplant Duplex Protocol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=KGFphcefwXA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V283</t>
+    <t xml:space="preserve">V290</t>
   </si>
   <si>
     <t xml:space="preserve">Doppler Imaging of Liver Transplants Diagnoses and Dilemmas</t>
@@ -6337,7 +6400,7 @@
     <t xml:space="preserve">https://www.youtube.com/watch?v=3El9mtbhkX4</t>
   </si>
   <si>
-    <t xml:space="preserve">V284</t>
+    <t xml:space="preserve">V291</t>
   </si>
   <si>
     <t xml:space="preserve">Orthotopic Liver Transplant Hepatic Artery and Portal Vein Complications</t>
@@ -6661,40 +6724,49 @@
     <t xml:space="preserve">24.1 da 3 ta dars yetarli</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=hbVxhOV6NFw</t>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=I4lJJs_eUGg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonographic evaluation of the liver transplant - Lecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=hbVxhOV6NFw</t>
   </si>
   <si>
     <t xml:space="preserve">Vascular ultrasound made simple</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1 da 3 ta dars yetarli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=kHKvcnuocFE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How to assess Subclavian steal syndrome by Ultrasound?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2 da yetarli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=QaQNYFjvKxs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POCUS: Differentiating the Aorta and IVC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7 da 3 ta dars yetarli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=LcuG9zdK4tM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venous ultrasound course: Identifying varicose veins in the insufficiency study (Medmastery)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6 da 3 ta dars yetarli</t>
+    <t xml:space="preserve">25-bobda yetarli dars bor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=TeGAC9MoZow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertebral Arteries &amp; Subclavian Steal (Path2Passing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=_DiApj4D3jc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carotid Artery Color/Spectral Doppler Ultrasound Normal Vs Abnormal Images</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=KArjnqDxBE0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplex ultrasound for Peripheral Artery Disease (Rama Surgery)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=-4tJgiWazjA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saphenous Vein Doppler Ultrasound Normal Vs Abnormal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=SHhKyEaW1NM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How To: Abdominal Ultrasound - Aorta Measurements (Sonosite)</t>
   </si>
   <si>
     <t xml:space="preserve">Kichik mavzular</t>
@@ -8629,7 +8701,7 @@
       </c>
       <c r="E29" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A29,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A29&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
@@ -12271,7 +12343,7 @@
       </c>
       <c r="E173" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A173,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A173&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
@@ -12296,7 +12368,7 @@
       </c>
       <c r="E174" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A174,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A174&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
@@ -12346,7 +12418,7 @@
       </c>
       <c r="E176" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A176,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A176&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
@@ -12446,7 +12518,7 @@
       </c>
       <c r="E180" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A180,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A180&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F180" s="6"/>
       <c r="G180" s="6"/>
@@ -13450,13 +13522,13 @@
       </c>
       <c r="E220" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A220,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A220&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F220" s="6"/>
       <c r="G220" s="6"/>
       <c r="H220" s="6" t="str">
         <f aca="false">IF(G220&lt;&gt;"","Takroriy",IF(E220=0,"Yetishmaydi",IF(F220="ha","Qisman to‘ldirilgan","Mavjud, lekin tekshirilmagan")))</f>
-        <v>Mavjud, lekin tekshirilmagan</v>
+        <v>Yetishmaydi</v>
       </c>
       <c r="I220" s="6"/>
     </row>
@@ -16501,7 +16573,7 @@
         <v>431</v>
       </c>
       <c r="C108" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>651</v>
@@ -16521,7 +16593,7 @@
         <v>433</v>
       </c>
       <c r="C109" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>651</v>
@@ -16561,7 +16633,7 @@
         <v>437</v>
       </c>
       <c r="C111" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>651</v>
@@ -16641,7 +16713,7 @@
         <v>445</v>
       </c>
       <c r="C115" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>651</v>
@@ -17108,7 +17180,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y285"/>
+  <dimension ref="A1:Y292"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -34544,10 +34616,10 @@
         <v>2048</v>
       </c>
       <c r="G270" s="6" t="s">
-        <v>2049</v>
+        <v>1194</v>
       </c>
       <c r="H270" s="6" t="s">
-        <v>2050</v>
+        <v>895</v>
       </c>
       <c r="I270" s="6" t="s">
         <v>812</v>
@@ -34559,10 +34631,10 @@
         <v>813</v>
       </c>
       <c r="L270" s="6" t="s">
-        <v>839</v>
+        <v>814</v>
       </c>
       <c r="M270" s="6" t="s">
-        <v>847</v>
+        <v>897</v>
       </c>
       <c r="N270" s="12" t="s">
         <v>816</v>
@@ -34588,29 +34660,31 @@
       </c>
       <c r="Y270" s="12"/>
     </row>
-    <row r="271" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="6" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="C271" s="6"/>
+      <c r="C271" s="6" t="s">
+        <v>107</v>
+      </c>
       <c r="D271" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B271,Mundarija!$A:$A,0)),"kod topilmadi")</f>
         <v>25.1. Qon tomirlarning normal sonografik anatomiyasi.</v>
       </c>
       <c r="E271" s="6" t="s">
+        <v>2050</v>
+      </c>
+      <c r="F271" s="11" t="s">
+        <v>2051</v>
+      </c>
+      <c r="G271" s="6" t="s">
         <v>2052</v>
       </c>
-      <c r="F271" s="11" t="s">
+      <c r="H271" s="6" t="s">
         <v>2053</v>
-      </c>
-      <c r="G271" s="6" t="s">
-        <v>1194</v>
-      </c>
-      <c r="H271" s="6" t="s">
-        <v>895</v>
       </c>
       <c r="I271" s="6" t="s">
         <v>812</v>
@@ -34622,10 +34696,10 @@
         <v>813</v>
       </c>
       <c r="L271" s="6" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="M271" s="6" t="s">
-        <v>897</v>
+        <v>847</v>
       </c>
       <c r="N271" s="12" t="s">
         <v>816</v>
@@ -34670,10 +34744,10 @@
         <v>2056</v>
       </c>
       <c r="G272" s="6" t="s">
-        <v>2057</v>
+        <v>1534</v>
       </c>
       <c r="H272" s="6" t="s">
-        <v>823</v>
+        <v>1592</v>
       </c>
       <c r="I272" s="6" t="s">
         <v>812</v>
@@ -34688,7 +34762,7 @@
         <v>839</v>
       </c>
       <c r="M272" s="6" t="s">
-        <v>847</v>
+        <v>826</v>
       </c>
       <c r="N272" s="12" t="s">
         <v>816</v>
@@ -34716,7 +34790,7 @@
     </row>
     <row r="273" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="6" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>432</v>
@@ -34727,16 +34801,16 @@
         <v>25.2. Karotid va vertebral arteriyalar.</v>
       </c>
       <c r="E273" s="6" t="s">
+        <v>2058</v>
+      </c>
+      <c r="F273" s="11" t="s">
         <v>2059</v>
       </c>
-      <c r="F273" s="11" t="s">
+      <c r="G273" s="6" t="s">
         <v>2060</v>
       </c>
-      <c r="G273" s="6" t="s">
+      <c r="H273" s="6" t="s">
         <v>2061</v>
-      </c>
-      <c r="H273" s="6" t="s">
-        <v>2062</v>
       </c>
       <c r="I273" s="6" t="s">
         <v>812</v>
@@ -34751,7 +34825,7 @@
         <v>1683</v>
       </c>
       <c r="M273" s="6" t="s">
-        <v>1648</v>
+        <v>847</v>
       </c>
       <c r="N273" s="12" t="s">
         <v>816</v>
@@ -34779,7 +34853,7 @@
     </row>
     <row r="274" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="6" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>434</v>
@@ -34790,16 +34864,16 @@
         <v>25.3. Aterosklerotik blyashkalar, stenoz va okklyuziya.</v>
       </c>
       <c r="E274" s="6" t="s">
+        <v>2063</v>
+      </c>
+      <c r="F274" s="11" t="s">
         <v>2064</v>
       </c>
-      <c r="F274" s="11" t="s">
+      <c r="G274" s="6" t="s">
         <v>2065</v>
       </c>
-      <c r="G274" s="6" t="s">
+      <c r="H274" s="6" t="s">
         <v>2066</v>
-      </c>
-      <c r="H274" s="6" t="s">
-        <v>2067</v>
       </c>
       <c r="I274" s="6" t="s">
         <v>812</v>
@@ -34842,7 +34916,7 @@
     </row>
     <row r="275" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="6" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>434</v>
@@ -34853,10 +34927,10 @@
         <v>25.3. Aterosklerotik blyashkalar, stenoz va okklyuziya.</v>
       </c>
       <c r="E275" s="6" t="s">
+        <v>2068</v>
+      </c>
+      <c r="F275" s="11" t="s">
         <v>2069</v>
-      </c>
-      <c r="F275" s="11" t="s">
-        <v>2070</v>
       </c>
       <c r="G275" s="6" t="s">
         <v>2044</v>
@@ -34877,7 +34951,7 @@
         <v>839</v>
       </c>
       <c r="M275" s="6" t="s">
-        <v>1648</v>
+        <v>847</v>
       </c>
       <c r="N275" s="12" t="s">
         <v>816</v>
@@ -34905,27 +34979,27 @@
     </row>
     <row r="276" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="6" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C276" s="6"/>
       <c r="D276" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B276,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.6. Yuzaki venalar va varikoz.</v>
+        <v>25.4. Yuqori va pastki ekstremita arteriyalari.</v>
       </c>
       <c r="E276" s="6" t="s">
+        <v>2071</v>
+      </c>
+      <c r="F276" s="11" t="s">
         <v>2072</v>
       </c>
-      <c r="F276" s="11" t="s">
-        <v>2073</v>
-      </c>
       <c r="G276" s="6" t="s">
-        <v>2044</v>
+        <v>1563</v>
       </c>
       <c r="H276" s="6" t="s">
-        <v>2045</v>
+        <v>1115</v>
       </c>
       <c r="I276" s="6" t="s">
         <v>812</v>
@@ -34940,7 +35014,7 @@
         <v>839</v>
       </c>
       <c r="M276" s="6" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="N276" s="12" t="s">
         <v>816</v>
@@ -34968,27 +35042,27 @@
     </row>
     <row r="277" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="6" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C277" s="6"/>
       <c r="D277" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B277,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.6. Yuzaki venalar va varikoz.</v>
+        <v>25.4. Yuqori va pastki ekstremita arteriyalari.</v>
       </c>
       <c r="E277" s="6" t="s">
+        <v>2074</v>
+      </c>
+      <c r="F277" s="11" t="s">
         <v>2075</v>
       </c>
-      <c r="F277" s="11" t="s">
-        <v>2076</v>
-      </c>
       <c r="G277" s="6" t="s">
-        <v>2044</v>
+        <v>822</v>
       </c>
       <c r="H277" s="6" t="s">
-        <v>2045</v>
+        <v>2037</v>
       </c>
       <c r="I277" s="6" t="s">
         <v>812</v>
@@ -35000,7 +35074,7 @@
         <v>813</v>
       </c>
       <c r="L277" s="6" t="s">
-        <v>839</v>
+        <v>814</v>
       </c>
       <c r="M277" s="6" t="s">
         <v>826</v>
@@ -35031,29 +35105,29 @@
     </row>
     <row r="278" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="6" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D278" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B278,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.6. Yuzaki venalar va varikoz.</v>
+        <v>25.4. Yuqori va pastki ekstremita arteriyalari.</v>
       </c>
       <c r="E278" s="6" t="s">
+        <v>2077</v>
+      </c>
+      <c r="F278" s="11" t="s">
         <v>2078</v>
       </c>
-      <c r="F278" s="11" t="s">
-        <v>2079</v>
-      </c>
       <c r="G278" s="6" t="s">
-        <v>2049</v>
+        <v>1158</v>
       </c>
       <c r="H278" s="6" t="s">
-        <v>2050</v>
+        <v>1777</v>
       </c>
       <c r="I278" s="6" t="s">
         <v>812</v>
@@ -35096,29 +35170,27 @@
     </row>
     <row r="279" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="6" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="C279" s="6" t="s">
-        <v>251</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="C279" s="6"/>
       <c r="D279" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B279,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.7. Qorin aortasi va pastki kava vena.</v>
+        <v>25.6. Yuzaki venalar va varikoz.</v>
       </c>
       <c r="E279" s="6" t="s">
+        <v>2080</v>
+      </c>
+      <c r="F279" s="11" t="s">
         <v>2081</v>
       </c>
-      <c r="F279" s="11" t="s">
-        <v>2082</v>
-      </c>
       <c r="G279" s="6" t="s">
-        <v>2083</v>
+        <v>2044</v>
       </c>
       <c r="H279" s="6" t="s">
-        <v>2084</v>
+        <v>2045</v>
       </c>
       <c r="I279" s="6" t="s">
         <v>812</v>
@@ -35130,7 +35202,7 @@
         <v>813</v>
       </c>
       <c r="L279" s="6" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="M279" s="6" t="s">
         <v>826</v>
@@ -35161,29 +35233,27 @@
     </row>
     <row r="280" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="6" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="C280" s="6" t="s">
-        <v>2086</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="C280" s="6"/>
       <c r="D280" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B280,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.7. Qorin aortasi va pastki kava vena.</v>
+        <v>25.6. Yuzaki venalar va varikoz.</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>2087</v>
+        <v>2083</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
       <c r="G280" s="6" t="s">
-        <v>2083</v>
+        <v>2044</v>
       </c>
       <c r="H280" s="6" t="s">
-        <v>2084</v>
+        <v>2045</v>
       </c>
       <c r="I280" s="6" t="s">
         <v>812</v>
@@ -35195,7 +35265,7 @@
         <v>813</v>
       </c>
       <c r="L280" s="6" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="M280" s="6" t="s">
         <v>826</v>
@@ -35224,31 +35294,31 @@
       </c>
       <c r="Y280" s="12"/>
     </row>
-    <row r="281" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="6" t="s">
-        <v>2089</v>
+        <v>2085</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>251</v>
+        <v>438</v>
       </c>
       <c r="D281" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B281,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.7. Qorin aortasi va pastki kava vena.</v>
+        <v>25.6. Yuzaki venalar va varikoz.</v>
       </c>
       <c r="E281" s="6" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
       <c r="F281" s="11" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
       <c r="G281" s="6" t="s">
-        <v>1253</v>
+        <v>2052</v>
       </c>
       <c r="H281" s="6" t="s">
-        <v>1575</v>
+        <v>2053</v>
       </c>
       <c r="I281" s="6" t="s">
         <v>812</v>
@@ -35260,10 +35330,10 @@
         <v>813</v>
       </c>
       <c r="L281" s="6" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="M281" s="6" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="N281" s="12" t="s">
         <v>816</v>
@@ -35291,29 +35361,29 @@
     </row>
     <row r="282" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="6" t="s">
-        <v>2092</v>
+        <v>2088</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D282" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B282,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.9. Transplantat tomirlari.</v>
+        <v>25.7. Qorin aortasi va pastki kava vena.</v>
       </c>
       <c r="E282" s="6" t="s">
-        <v>2093</v>
+        <v>2089</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>2094</v>
+        <v>2090</v>
       </c>
       <c r="G282" s="6" t="s">
-        <v>844</v>
+        <v>1253</v>
       </c>
       <c r="H282" s="6" t="s">
-        <v>1784</v>
+        <v>1575</v>
       </c>
       <c r="I282" s="6" t="s">
         <v>812</v>
@@ -35325,10 +35395,10 @@
         <v>813</v>
       </c>
       <c r="L282" s="6" t="s">
-        <v>1683</v>
+        <v>814</v>
       </c>
       <c r="M282" s="6" t="s">
-        <v>847</v>
+        <v>826</v>
       </c>
       <c r="N282" s="12" t="s">
         <v>816</v>
@@ -35356,29 +35426,29 @@
     </row>
     <row r="283" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="6" t="s">
-        <v>2095</v>
+        <v>2091</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D283" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B283,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.9. Transplantat tomirlari.</v>
+        <v>25.7. Qorin aortasi va pastki kava vena.</v>
       </c>
       <c r="E283" s="6" t="s">
-        <v>2096</v>
+        <v>2092</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
       <c r="G283" s="6" t="s">
-        <v>822</v>
+        <v>2094</v>
       </c>
       <c r="H283" s="6" t="s">
-        <v>2037</v>
+        <v>2095</v>
       </c>
       <c r="I283" s="6" t="s">
         <v>812</v>
@@ -35390,7 +35460,7 @@
         <v>813</v>
       </c>
       <c r="L283" s="6" t="s">
-        <v>839</v>
+        <v>814</v>
       </c>
       <c r="M283" s="6" t="s">
         <v>826</v>
@@ -35421,29 +35491,29 @@
     </row>
     <row r="284" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="6" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="D284" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B284,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.9. Transplantat tomirlari.</v>
+        <v>25.7. Qorin aortasi va pastki kava vena.</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="G284" s="6" t="s">
-        <v>1170</v>
+        <v>2094</v>
       </c>
       <c r="H284" s="6" t="s">
-        <v>845</v>
+        <v>2095</v>
       </c>
       <c r="I284" s="6" t="s">
         <v>812</v>
@@ -35455,10 +35525,10 @@
         <v>813</v>
       </c>
       <c r="L284" s="6" t="s">
-        <v>1683</v>
+        <v>814</v>
       </c>
       <c r="M284" s="6" t="s">
-        <v>847</v>
+        <v>826</v>
       </c>
       <c r="N284" s="12" t="s">
         <v>816</v>
@@ -35486,29 +35556,27 @@
     </row>
     <row r="285" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="6" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="C285" s="6" t="s">
-        <v>446</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="C285" s="6"/>
       <c r="D285" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B285,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>10.8. Jigar transplantatini tekshirish.</v>
+        <v>25.8. Gemodializ arteriovenoz kirish yo‘llari.</v>
       </c>
       <c r="E285" s="6" t="s">
+        <v>2100</v>
+      </c>
+      <c r="F285" s="11" t="s">
+        <v>2101</v>
+      </c>
+      <c r="G285" s="6" t="s">
+        <v>1344</v>
+      </c>
+      <c r="H285" s="6" t="s">
         <v>2102</v>
-      </c>
-      <c r="F285" s="11" t="s">
-        <v>2103</v>
-      </c>
-      <c r="G285" s="6" t="s">
-        <v>1170</v>
-      </c>
-      <c r="H285" s="6" t="s">
-        <v>845</v>
       </c>
       <c r="I285" s="6" t="s">
         <v>812</v>
@@ -35549,10 +35617,459 @@
       </c>
       <c r="Y285" s="12"/>
     </row>
+    <row r="286" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="6" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="C286" s="6"/>
+      <c r="D286" s="6" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B286,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.8. Gemodializ arteriovenoz kirish yo‘llari.</v>
+      </c>
+      <c r="E286" s="6" t="s">
+        <v>2104</v>
+      </c>
+      <c r="F286" s="11" t="s">
+        <v>2105</v>
+      </c>
+      <c r="G286" s="6" t="s">
+        <v>2052</v>
+      </c>
+      <c r="H286" s="6" t="s">
+        <v>2053</v>
+      </c>
+      <c r="I286" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="J286" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="K286" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="L286" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="M286" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="N286" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="O286" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="P286" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q286" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="R286" s="12"/>
+      <c r="S286" s="12"/>
+      <c r="T286" s="12"/>
+      <c r="U286" s="12"/>
+      <c r="V286" s="12"/>
+      <c r="W286" s="12"/>
+      <c r="X286" s="6" t="str">
+        <f aca="false">IF(COUNT(R286:W286)=6,SUM(R286:W286),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y286" s="12"/>
+    </row>
+    <row r="287" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="6" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="C287" s="6"/>
+      <c r="D287" s="6" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B287,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.8. Gemodializ arteriovenoz kirish yo‘llari.</v>
+      </c>
+      <c r="E287" s="6" t="s">
+        <v>2107</v>
+      </c>
+      <c r="F287" s="11" t="s">
+        <v>2108</v>
+      </c>
+      <c r="G287" s="6" t="s">
+        <v>1601</v>
+      </c>
+      <c r="H287" s="6" t="s">
+        <v>1602</v>
+      </c>
+      <c r="I287" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="J287" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="K287" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="L287" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="M287" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="N287" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="O287" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="P287" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q287" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="R287" s="12"/>
+      <c r="S287" s="12"/>
+      <c r="T287" s="12"/>
+      <c r="U287" s="12"/>
+      <c r="V287" s="12"/>
+      <c r="W287" s="12"/>
+      <c r="X287" s="6" t="str">
+        <f aca="false">IF(COUNT(R287:W287)=6,SUM(R287:W287),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y287" s="12"/>
+    </row>
+    <row r="288" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="6" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D288" s="6" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B288,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.9. Transplantat tomirlari.</v>
+      </c>
+      <c r="E288" s="6" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F288" s="11" t="s">
+        <v>2111</v>
+      </c>
+      <c r="G288" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="H288" s="6" t="s">
+        <v>2037</v>
+      </c>
+      <c r="I288" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="J288" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="K288" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="L288" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="M288" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="N288" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="O288" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="P288" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q288" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="R288" s="12"/>
+      <c r="S288" s="12"/>
+      <c r="T288" s="12"/>
+      <c r="U288" s="12"/>
+      <c r="V288" s="12"/>
+      <c r="W288" s="12"/>
+      <c r="X288" s="6" t="str">
+        <f aca="false">IF(COUNT(R288:W288)=6,SUM(R288:W288),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y288" s="12"/>
+    </row>
+    <row r="289" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="6" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D289" s="6" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B289,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.9. Transplantat tomirlari.</v>
+      </c>
+      <c r="E289" s="6" t="s">
+        <v>2113</v>
+      </c>
+      <c r="F289" s="11" t="s">
+        <v>2114</v>
+      </c>
+      <c r="G289" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="H289" s="6" t="s">
+        <v>1784</v>
+      </c>
+      <c r="I289" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="J289" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="K289" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="L289" s="6" t="s">
+        <v>1683</v>
+      </c>
+      <c r="M289" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="N289" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="O289" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="P289" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q289" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="R289" s="12"/>
+      <c r="S289" s="12"/>
+      <c r="T289" s="12"/>
+      <c r="U289" s="12"/>
+      <c r="V289" s="12"/>
+      <c r="W289" s="12"/>
+      <c r="X289" s="6" t="str">
+        <f aca="false">IF(COUNT(R289:W289)=6,SUM(R289:W289),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y289" s="12"/>
+    </row>
+    <row r="290" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="6" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="C290" s="6"/>
+      <c r="D290" s="6" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B290,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.2. Karotid va vertebral arteriyalar.</v>
+      </c>
+      <c r="E290" s="6" t="s">
+        <v>2116</v>
+      </c>
+      <c r="F290" s="11" t="s">
+        <v>2117</v>
+      </c>
+      <c r="G290" s="6" t="s">
+        <v>2118</v>
+      </c>
+      <c r="H290" s="6" t="s">
+        <v>823</v>
+      </c>
+      <c r="I290" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="J290" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="K290" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="L290" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="M290" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="N290" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="O290" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="P290" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q290" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="R290" s="12"/>
+      <c r="S290" s="12"/>
+      <c r="T290" s="12"/>
+      <c r="U290" s="12"/>
+      <c r="V290" s="12"/>
+      <c r="W290" s="12"/>
+      <c r="X290" s="6" t="str">
+        <f aca="false">IF(COUNT(R290:W290)=6,SUM(R290:W290),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y290" s="12"/>
+    </row>
+    <row r="291" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="6" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D291" s="6" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B291,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.9. Transplantat tomirlari.</v>
+      </c>
+      <c r="E291" s="6" t="s">
+        <v>2120</v>
+      </c>
+      <c r="F291" s="11" t="s">
+        <v>2121</v>
+      </c>
+      <c r="G291" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H291" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="I291" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="J291" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="K291" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="L291" s="6" t="s">
+        <v>1683</v>
+      </c>
+      <c r="M291" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="N291" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="O291" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="P291" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q291" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="R291" s="12"/>
+      <c r="S291" s="12"/>
+      <c r="T291" s="12"/>
+      <c r="U291" s="12"/>
+      <c r="V291" s="12"/>
+      <c r="W291" s="12"/>
+      <c r="X291" s="6" t="str">
+        <f aca="false">IF(COUNT(R291:W291)=6,SUM(R291:W291),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y291" s="12"/>
+    </row>
+    <row r="292" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="6" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="D292" s="6" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B292,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>10.8. Jigar transplantatini tekshirish.</v>
+      </c>
+      <c r="E292" s="6" t="s">
+        <v>2123</v>
+      </c>
+      <c r="F292" s="11" t="s">
+        <v>2124</v>
+      </c>
+      <c r="G292" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H292" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="I292" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="J292" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="K292" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="L292" s="6" t="s">
+        <v>1683</v>
+      </c>
+      <c r="M292" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="N292" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="O292" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="P292" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q292" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="R292" s="12"/>
+      <c r="S292" s="12"/>
+      <c r="T292" s="12"/>
+      <c r="U292" s="12"/>
+      <c r="V292" s="12"/>
+      <c r="W292" s="12"/>
+      <c r="X292" s="6" t="str">
+        <f aca="false">IF(COUNT(R292:W292)=6,SUM(R292:W292),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y292" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y285"/>
+  <autoFilter ref="A1:Y292"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="0 dan 5 gacha butun son" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:W485" type="whole">
+    <dataValidation allowBlank="true" error="0 dan 5 gacha butun son" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:W492" type="whole">
       <formula1>0</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -35826,22 +36343,29 @@
     <hyperlink ref="F267" r:id="rId266" display="https://www.youtube.com/watch?v=I2vhPP1VgkA"/>
     <hyperlink ref="F268" r:id="rId267" display="https://www.youtube.com/watch?v=ADQxr0da_yk"/>
     <hyperlink ref="F269" r:id="rId268" display="https://www.youtube.com/watch?v=ihXKv9qqbZw"/>
-    <hyperlink ref="F270" r:id="rId269" display="https://www.youtube.com/watch?v=X739XUv0xkE"/>
-    <hyperlink ref="F271" r:id="rId270" display="https://www.youtube.com/watch?v=IaejYqKM6mI"/>
-    <hyperlink ref="F272" r:id="rId271" display="https://www.youtube.com/watch?v=TeGAC9MoZow"/>
+    <hyperlink ref="F270" r:id="rId269" display="https://www.youtube.com/watch?v=IaejYqKM6mI"/>
+    <hyperlink ref="F271" r:id="rId270" display="https://www.youtube.com/watch?v=X739XUv0xkE"/>
+    <hyperlink ref="F272" r:id="rId271" display="https://www.youtube.com/watch?v=_CAkI846j7E"/>
     <hyperlink ref="F273" r:id="rId272" display="https://www.youtube.com/watch?v=dRVXK3DjBzk"/>
     <hyperlink ref="F274" r:id="rId273" display="https://www.youtube.com/watch?v=pXjCmheNuug"/>
     <hyperlink ref="F275" r:id="rId274" display="https://www.youtube.com/watch?v=76hyW1-XkGk"/>
-    <hyperlink ref="F276" r:id="rId275" display="https://www.youtube.com/watch?v=n5HblR27soE"/>
-    <hyperlink ref="F277" r:id="rId276" display="https://www.youtube.com/watch?v=QFDDU7lpsuA"/>
-    <hyperlink ref="F278" r:id="rId277" display="https://www.youtube.com/watch?v=KLt-sO1G74A"/>
-    <hyperlink ref="F279" r:id="rId278" display="https://www.youtube.com/watch?v=w8wc8-40F1E"/>
-    <hyperlink ref="F280" r:id="rId279" display="https://www.youtube.com/watch?v=Flc8xS2foOU"/>
-    <hyperlink ref="F281" r:id="rId280" display="https://www.youtube.com/watch?v=IbSW2GCMsoQ"/>
-    <hyperlink ref="F282" r:id="rId281" display="https://www.youtube.com/watch?v=eNsLjk2fJxc"/>
-    <hyperlink ref="F283" r:id="rId282" display="https://www.youtube.com/watch?v=KGFphcefwXA"/>
-    <hyperlink ref="F284" r:id="rId283" display="https://www.youtube.com/watch?v=3El9mtbhkX4"/>
-    <hyperlink ref="F285" r:id="rId284" display="https://www.youtube.com/watch?v=jF22GbTfFS4"/>
+    <hyperlink ref="F276" r:id="rId275" display="https://www.youtube.com/watch?v=4JyRA2xSQ6o"/>
+    <hyperlink ref="F277" r:id="rId276" display="https://www.youtube.com/watch?v=J4z7BCopSvs"/>
+    <hyperlink ref="F278" r:id="rId277" display="https://www.youtube.com/watch?v=Vf7nE0vBSco"/>
+    <hyperlink ref="F279" r:id="rId278" display="https://www.youtube.com/watch?v=n5HblR27soE"/>
+    <hyperlink ref="F280" r:id="rId279" display="https://www.youtube.com/watch?v=QFDDU7lpsuA"/>
+    <hyperlink ref="F281" r:id="rId280" display="https://www.youtube.com/watch?v=KLt-sO1G74A"/>
+    <hyperlink ref="F282" r:id="rId281" display="https://www.youtube.com/watch?v=IbSW2GCMsoQ"/>
+    <hyperlink ref="F283" r:id="rId282" display="https://www.youtube.com/watch?v=w8wc8-40F1E"/>
+    <hyperlink ref="F284" r:id="rId283" display="https://www.youtube.com/watch?v=Flc8xS2foOU"/>
+    <hyperlink ref="F285" r:id="rId284" display="https://www.youtube.com/watch?v=EjXcrvJTmYw"/>
+    <hyperlink ref="F286" r:id="rId285" display="https://www.youtube.com/watch?v=cFHfoL1k_pk"/>
+    <hyperlink ref="F287" r:id="rId286" display="https://www.youtube.com/watch?v=-8VG1bBhchI"/>
+    <hyperlink ref="F288" r:id="rId287" display="https://www.youtube.com/watch?v=KGFphcefwXA"/>
+    <hyperlink ref="F289" r:id="rId288" display="https://www.youtube.com/watch?v=eNsLjk2fJxc"/>
+    <hyperlink ref="F290" r:id="rId289" display="https://www.youtube.com/watch?v=TeGAC9MoZow"/>
+    <hyperlink ref="F291" r:id="rId290" display="https://www.youtube.com/watch?v=3El9mtbhkX4"/>
+    <hyperlink ref="F292" r:id="rId291" display="https://www.youtube.com/watch?v=jF22GbTfFS4"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -35850,7 +36374,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId285"/>
+  <drawing r:id="rId292"/>
 </worksheet>
 </file>
 
@@ -35859,7 +36383,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -35872,195 +36396,195 @@
         <v>746</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>2104</v>
+        <v>2125</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2105</v>
+        <v>2126</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2106</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>2107</v>
+        <v>2128</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2108</v>
+        <v>2129</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2109</v>
+        <v>2130</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2110</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>2111</v>
+        <v>2132</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2112</v>
+        <v>2133</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>2113</v>
+        <v>2134</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>2110</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>2114</v>
+        <v>2135</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2115</v>
+        <v>2136</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>2116</v>
+        <v>2137</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>2110</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>2117</v>
+        <v>2138</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2118</v>
+        <v>2139</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>2119</v>
+        <v>2140</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>2110</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>2120</v>
+        <v>2141</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2121</v>
+        <v>2142</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>2122</v>
+        <v>2143</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2123</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>2124</v>
+        <v>2145</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>2125</v>
+        <v>2146</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>2126</v>
+        <v>2147</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>2127</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>2128</v>
+        <v>2149</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>2129</v>
+        <v>2150</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>2130</v>
+        <v>2151</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>2127</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>2131</v>
+        <v>2152</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>2132</v>
+        <v>2153</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>2133</v>
+        <v>2154</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>2135</v>
+        <v>2156</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>2136</v>
+        <v>2157</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>2137</v>
+        <v>2158</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>2138</v>
+        <v>2159</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>2139</v>
+        <v>2160</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>2140</v>
+        <v>2161</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>2141</v>
+        <v>2162</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>2142</v>
+        <v>2163</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>2143</v>
+        <v>2164</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>2123</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>2144</v>
+        <v>2165</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>2145</v>
+        <v>2166</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>2146</v>
+        <v>2167</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>2147</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>2148</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>2149</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>2150</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>2127</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36071,10 +36595,10 @@
         <v>962</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>2151</v>
+        <v>2172</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>2152</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36085,10 +36609,10 @@
         <v>1054</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>2151</v>
+        <v>2172</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>2152</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36099,388 +36623,430 @@
         <v>1060</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>2151</v>
+        <v>2172</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>2152</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>2153</v>
+        <v>2174</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>2175</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>2154</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>2133</v>
-      </c>
       <c r="D18" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>2158</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>2155</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>2156</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>2137</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>2134</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>2157</v>
+        <v>2178</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>2158</v>
+        <v>2179</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>2159</v>
+        <v>2180</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>2127</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>2160</v>
+        <v>2181</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>2161</v>
+        <v>2182</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>2162</v>
+        <v>2183</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>2127</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>2163</v>
+        <v>2184</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>2164</v>
+        <v>2185</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>2165</v>
+        <v>2186</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>2166</v>
+        <v>2187</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>2167</v>
+        <v>2188</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>2165</v>
+        <v>2186</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>2168</v>
+        <v>2189</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>2169</v>
+        <v>2190</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>2165</v>
+        <v>2186</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>2170</v>
+        <v>2191</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>2171</v>
+        <v>2192</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>2172</v>
+        <v>2193</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>2173</v>
+        <v>2194</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>2174</v>
+        <v>2195</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>2175</v>
+        <v>2196</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>2176</v>
+        <v>2197</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>2177</v>
+        <v>2198</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>2178</v>
+        <v>2199</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>2127</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>2179</v>
+        <v>2200</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>2180</v>
+        <v>2201</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>2181</v>
+        <v>2202</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>2127</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>2182</v>
+        <v>2203</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>2183</v>
+        <v>2204</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>2184</v>
+        <v>2205</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>2127</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>2185</v>
+        <v>2206</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>2186</v>
+        <v>2207</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>2172</v>
+        <v>2193</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>2187</v>
+        <v>2208</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>2188</v>
+        <v>2209</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>2165</v>
+        <v>2186</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>2189</v>
+        <v>2210</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>2190</v>
+        <v>2211</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>2165</v>
+        <v>2186</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>2191</v>
+        <v>2212</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>2192</v>
+        <v>2213</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>2172</v>
+        <v>2193</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>2193</v>
+        <v>2214</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>2194</v>
+        <v>2215</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>2165</v>
+        <v>2186</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>2195</v>
+        <v>2216</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>2196</v>
+        <v>2217</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>2172</v>
+        <v>2193</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>2197</v>
+        <v>2218</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>2198</v>
+        <v>2219</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>2172</v>
+        <v>2193</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>2199</v>
+        <v>2220</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>2200</v>
+        <v>2221</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>2172</v>
+        <v>2193</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>2201</v>
+        <v>2222</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>2202</v>
+        <v>2223</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>2175</v>
+        <v>2196</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>2134</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>2203</v>
+        <v>2224</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>2204</v>
+        <v>2225</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>2205</v>
+        <v>2226</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>2127</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>2206</v>
+        <v>2227</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>2207</v>
+        <v>2228</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>2208</v>
+        <v>2229</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>2127</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>2209</v>
+        <v>2230</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>2210</v>
+        <v>2231</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>2211</v>
+        <v>2186</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>2127</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>2212</v>
+        <v>2232</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>2213</v>
+        <v>2233</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>2214</v>
+        <v>2234</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>2127</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>2215</v>
+        <v>2235</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>2216</v>
+        <v>2236</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>2217</v>
+        <v>2234</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>2127</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>2218</v>
+        <v>2237</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>2219</v>
+        <v>2238</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>2220</v>
+        <v>2234</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>2127</v>
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="11" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="11" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="11" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>2148</v>
       </c>
     </row>
   </sheetData>
@@ -36524,10 +37090,13 @@
     <hyperlink ref="A38" r:id="rId37" display="https://www.youtube.com/watch?v=NXdmwnSjhx8"/>
     <hyperlink ref="A39" r:id="rId38" display="https://www.youtube.com/watch?v=UtgJ85-OdHM"/>
     <hyperlink ref="A40" r:id="rId39" display="https://www.youtube.com/watch?v=poGrtzLVDLk"/>
-    <hyperlink ref="A41" r:id="rId40" display="https://www.youtube.com/watch?v=hbVxhOV6NFw"/>
-    <hyperlink ref="A42" r:id="rId41" display="https://www.youtube.com/watch?v=kHKvcnuocFE"/>
-    <hyperlink ref="A43" r:id="rId42" display="https://www.youtube.com/watch?v=QaQNYFjvKxs"/>
-    <hyperlink ref="A44" r:id="rId43" display="https://www.youtube.com/watch?v=LcuG9zdK4tM"/>
+    <hyperlink ref="A41" r:id="rId40" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=I4lJJs_eUGg"/>
+    <hyperlink ref="A42" r:id="rId41" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=hbVxhOV6NFw"/>
+    <hyperlink ref="A43" r:id="rId42" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=TeGAC9MoZow"/>
+    <hyperlink ref="A44" r:id="rId43" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=_DiApj4D3jc"/>
+    <hyperlink ref="A45" r:id="rId44" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=KArjnqDxBE0"/>
+    <hyperlink ref="A46" r:id="rId45" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=-4tJgiWazjA"/>
+    <hyperlink ref="A47" r:id="rId46" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=SHhKyEaW1NM"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -36563,22 +37132,22 @@
         <v>36</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2221</v>
+        <v>2245</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2222</v>
+        <v>2246</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>2223</v>
+        <v>2247</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2224</v>
+        <v>2248</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2225</v>
+        <v>2249</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>2147</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37490,15 +38059,15 @@
       </c>
       <c r="D30" s="6" t="n">
         <f aca="false">COUNTIFS(Mundarija!$C$2:$C$254,B30,Mundarija!$E$2:$E$254,"&gt;0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="15" t="n">
         <f aca="false">IF(C30=0,0,D30/C30)</f>
-        <v>0.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="F30" s="6" t="n">
         <f aca="false">COUNTIFS(Mundarija!$C$2:$C$254,B30,Mundarija!$H$2:$H$254,"Yetishmaydi")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G30" s="6" t="n">
         <f aca="false">COUNTIFS(Mundarija!$C$2:$C$254,B30,Mundarija!$H$2:$H$254,"Qisman to‘ldirilgan")</f>
@@ -37640,7 +38209,7 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="16"/>
       <c r="B35" s="16" t="s">
-        <v>2226</v>
+        <v>2250</v>
       </c>
       <c r="C35" s="16" t="n">
         <f aca="false">SUM(C2:C34)</f>
@@ -37648,15 +38217,15 @@
       </c>
       <c r="D35" s="16" t="n">
         <f aca="false">SUM(D2:D34)</f>
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E35" s="17" t="n">
         <f aca="false">IF(C35=0,0,D35/C35)</f>
-        <v>0.707509881422925</v>
+        <v>0.703557312252965</v>
       </c>
       <c r="F35" s="16" t="n">
         <f aca="false">SUM(F2:F34)</f>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G35" s="16" t="n">
         <f aca="false">SUM(G2:G34)</f>
@@ -37669,26 +38238,26 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>2227</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>2228</v>
+        <v>2252</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>2229</v>
+        <v>2253</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>2230</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>2231</v>
+        <v>2255</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>2232</v>
+        <v>2256</v>
       </c>
       <c r="C39" s="15" t="n">
         <f aca="false">C35/253</f>
@@ -37697,22 +38266,22 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>2233</v>
+        <v>2257</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>2234</v>
+        <v>2258</v>
       </c>
       <c r="C40" s="15" t="n">
         <f aca="false">E35</f>
-        <v>0.707509881422925</v>
+        <v>0.703557312252965</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>2235</v>
+        <v>2259</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>2236</v>
+        <v>2260</v>
       </c>
       <c r="C41" s="15" t="n">
         <f aca="false">SUM(D2:D7)/SUM(C2:C7)</f>
@@ -37721,25 +38290,25 @@
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>2237</v>
+        <v>2261</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>2238</v>
+        <v>2262</v>
       </c>
       <c r="C42" s="15" t="n">
-        <f aca="false">(COUNTIF(Katalog!$Q$2:$Q$285,"Havola tekshirilgan*")+COUNTIF(Katalog!$Q$2:$Q$285,"Metadata tekshirilgan*"))/COUNTA(Katalog!$A$2:$A$285)</f>
-        <v>0.98943661971831</v>
+        <f aca="false">(COUNTIF(Katalog!$Q$2:$Q$292,"Havola tekshirilgan*")+COUNTIF(Katalog!$Q$2:$Q$292,"Metadata tekshirilgan*"))/COUNTA(Katalog!$A$2:$A$292)</f>
+        <v>0.989690721649485</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>2239</v>
+        <v>2263</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>2240</v>
+        <v>2264</v>
       </c>
       <c r="C43" s="15" t="n">
-        <f aca="false">COUNT(Katalog!$X$2:$X$285)/COUNTA(Katalog!$A$2:$A$285)</f>
+        <f aca="false">COUNT(Katalog!$X$2:$X$292)/COUNTA(Katalog!$A$2:$A$292)</f>
         <v>0</v>
       </c>
     </row>
@@ -37771,400 +38340,400 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>2241</v>
+        <v>2265</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>2242</v>
+        <v>2266</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2243</v>
+        <v>2267</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>2244</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>2245</v>
+        <v>2269</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2246</v>
+        <v>2270</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2247</v>
+        <v>2271</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2248</v>
+        <v>2272</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>2249</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2250</v>
+        <v>2274</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2251</v>
+        <v>2275</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>2252</v>
+        <v>2276</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>2253</v>
+        <v>2277</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>2254</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2255</v>
+        <v>2279</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2256</v>
+        <v>2280</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>2257</v>
+        <v>2281</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>2258</v>
+        <v>2282</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>2259</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2260</v>
+        <v>2284</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2261</v>
+        <v>2285</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>2262</v>
+        <v>2286</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>2258</v>
+        <v>2282</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>2263</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2264</v>
+        <v>2288</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2265</v>
+        <v>2289</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>2266</v>
+        <v>2290</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2258</v>
+        <v>2282</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>2267</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2268</v>
+        <v>2292</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>2269</v>
+        <v>2293</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>2270</v>
+        <v>2294</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>2258</v>
+        <v>2282</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>2271</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>2272</v>
+        <v>2296</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>2273</v>
+        <v>2297</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>2274</v>
+        <v>2298</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>2275</v>
+        <v>2299</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>2276</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2277</v>
+        <v>2301</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>2278</v>
+        <v>2302</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2280</v>
+        <v>2304</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>2281</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>2282</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>2283</v>
+        <v>2307</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>2284</v>
+        <v>2308</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2105</v>
+        <v>2126</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>2285</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>2286</v>
+        <v>2310</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>2287</v>
+        <v>2311</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>2288</v>
+        <v>2312</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>2289</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>2286</v>
+        <v>2310</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>2290</v>
+        <v>2314</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>2291</v>
+        <v>2315</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>2292</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>2286</v>
+        <v>2310</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>2293</v>
+        <v>2317</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>2294</v>
+        <v>2318</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>2295</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>2286</v>
+        <v>2310</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>2296</v>
+        <v>2320</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>2297</v>
+        <v>2321</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>2298</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>2286</v>
+        <v>2310</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>2299</v>
+        <v>2323</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>2300</v>
+        <v>2324</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>2301</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>2286</v>
+        <v>2310</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>2302</v>
+        <v>2326</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>2303</v>
+        <v>2327</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>2304</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>2305</v>
+        <v>2329</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>95</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>2306</v>
+        <v>2330</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>2307</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>2308</v>
+        <v>2332</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>63</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>2309</v>
+        <v>2333</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>2310</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>2308</v>
+        <v>2332</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>2311</v>
+        <v>2335</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>2312</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>2308</v>
+        <v>2332</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>2313</v>
+        <v>2337</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>2314</v>
+        <v>2338</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>2315</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>2308</v>
+        <v>2332</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>2316</v>
+        <v>2340</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>2317</v>
+        <v>2341</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>2318</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>2224</v>
+        <v>2248</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>2319</v>
+        <v>2343</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>2320</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>2224</v>
+        <v>2248</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>201</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>2321</v>
+        <v>2345</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>2322</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>2224</v>
+        <v>2248</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>354</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>2323</v>
+        <v>2347</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>2324</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>2325</v>
+        <v>2349</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>482</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>2326</v>
+        <v>2350</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>2327</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>2328</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>2329</v>
+        <v>2353</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>2330</v>
+        <v>2354</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>2331</v>
+        <v>2355</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>41</v>
@@ -38172,86 +38741,86 @@
     </row>
     <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>2332</v>
+        <v>2356</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>2333</v>
+        <v>2357</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>2334</v>
+        <v>2358</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>2335</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>2336</v>
+        <v>2360</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>2337</v>
+        <v>2361</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>2338</v>
+        <v>2362</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>2335</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>2339</v>
+        <v>2363</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>2340</v>
+        <v>2364</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>2341</v>
+        <v>2365</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>2342</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>2343</v>
+        <v>2367</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>2344</v>
+        <v>2368</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>2345</v>
+        <v>2369</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>2346</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>2347</v>
+        <v>2371</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>2348</v>
+        <v>2372</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>2349</v>
+        <v>2373</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>2350</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>2351</v>
+        <v>2375</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>2352</v>
+        <v>2376</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>2353</v>
+        <v>2377</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>2354</v>
+        <v>2378</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
+++ b/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Audit" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Katalog!$A$1:$Y$292</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Katalog!$A$1:$Y$286</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Mundarija!$A$1:$I$254</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Qidiruv navbati'!$A$1:$F$117</definedName>
   </definedNames>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6809" uniqueCount="2379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6705" uniqueCount="2364">
   <si>
     <t xml:space="preserve">SHOKALON — videodarslar katalogi, 7-versiya</t>
   </si>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Nima bor</t>
   </si>
   <si>
-    <t xml:space="preserve">33 bob, 253 kichik mavzu (Mundarija); 291 ta video (Katalog) — ilovadagi barcha darslar shu yerda kod va Video ID bilan; rad etilgan havolalar; bob bo‘yicha qamrov; audit va loyihadan chetga chiqishlar.</t>
+    <t xml:space="preserve">33 bob, 253 kichik mavzu (Mundarija); 285 ta video (Katalog) — ilovadagi barcha darslar shu yerda kod va Video ID bilan; rad etilgan havolalar; bob bo‘yicha qamrov; audit va loyihadan chetga chiqishlar.</t>
   </si>
   <si>
     <t xml:space="preserve">Mavzu kodi</t>
@@ -2212,16 +2212,16 @@
     <t xml:space="preserve">carotid duplex protocol; vertebral artery ultrasound; subclavian steal</t>
   </si>
   <si>
-    <t xml:space="preserve">carotid stenosis criteria SRU IAC; carotid plaque ultrasound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lower extremity arterial duplex; peripheral arterial disease ultrasound</t>
+    <t xml:space="preserve">carotid stenosis criteria SRU IAC; carotid plaque characterization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lower extremity arterial duplex; upper extremity arterial ultrasound; ABI</t>
   </si>
   <si>
     <t xml:space="preserve">DVT compression ultrasound; lower limb venous duplex</t>
   </si>
   <si>
-    <t xml:space="preserve">varicose veins reflux ultrasound; great saphenous vein insufficiency</t>
+    <t xml:space="preserve">venous reflux ultrasound; great saphenous vein mapping; varicose veins</t>
   </si>
   <si>
     <t xml:space="preserve">abdominal aorta ultrasound; IVC ultrasound</t>
@@ -2230,10 +2230,10 @@
     <t xml:space="preserve">dialysis fistula ultrasound; AV access duplex</t>
   </si>
   <si>
-    <t xml:space="preserve">renal transplant Doppler; liver transplant Doppler complications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transcranial Doppler TCD basics</t>
+    <t xml:space="preserve">transplant Doppler ultrasound liver kidney vascular complications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transcranial Doppler technique; TCD windows</t>
   </si>
   <si>
     <t xml:space="preserve">Bo‘limlar holati</t>
@@ -6193,16 +6193,22 @@
     <t xml:space="preserve">PAHO TV</t>
   </si>
   <si>
-    <t xml:space="preserve">Xalqaro sog‘liqni saqlash tashkiloti (PAHO/WHO) vebinari; tili tekshirilmagan (nomi inglizcha)</t>
+    <t xml:space="preserve">Xalqaro sog‘liqni saqlash tashkiloti (PAHO/JSST)</t>
   </si>
   <si>
     <t xml:space="preserve">V271</t>
   </si>
   <si>
-    <t xml:space="preserve">Hot Tips - Finding the Vertebral Artery with Ultrasound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=_CAkI846j7E</t>
+    <t xml:space="preserve">Vertebral Arteries &amp; Subclavian Steal: Here's the Breakdown You Need by an Ultrasound Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=TeGAC9MoZow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path2Passing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imtihonga tayyorlov kanali (sonografist)</t>
   </si>
   <si>
     <t xml:space="preserve">V272</t>
@@ -6217,7 +6223,7 @@
     <t xml:space="preserve">Radcliffe Cardiology</t>
   </si>
   <si>
-    <t xml:space="preserve">Ta’lim kanali (Radcliffe Cardiology)</t>
+    <t xml:space="preserve">Ilmiy nashriyot (Radcliffe Cardiology)</t>
   </si>
   <si>
     <t xml:space="preserve">V273</t>
@@ -6247,73 +6253,88 @@
     <t xml:space="preserve">V275</t>
   </si>
   <si>
-    <t xml:space="preserve">How to Perform and Interpret Peripheral Arterial Doppler Examinations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=4JyRA2xSQ6o</t>
+    <t xml:space="preserve">Carotid Arterial Plaque by Ultrasound - Characterization of Atherosclerosis &amp; Evaluation of CV Risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=fC7gjgVx0LI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASE360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional jamiyat (ASE)</t>
   </si>
   <si>
     <t xml:space="preserve">V276</t>
   </si>
   <si>
-    <t xml:space="preserve">Upper Extremity Arterial Duplex Anatomy and Protocol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=J4z7BCopSvs</t>
+    <t xml:space="preserve">Duplex Scanning of the Subclavian Veins and Arteries (September 2018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=VYhlgQu-JOI</t>
   </si>
   <si>
     <t xml:space="preserve">V277</t>
   </si>
   <si>
-    <t xml:space="preserve">Interpreting duplex waveforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=Vf7nE0vBSco</t>
+    <t xml:space="preserve">Part 1: Varicose veins ultrasound assessment: GSV anatomy assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=n5HblR27soE</t>
   </si>
   <si>
     <t xml:space="preserve">V278</t>
   </si>
   <si>
-    <t xml:space="preserve">Part 1: Varicose veins ultrasound assessment: GSV anatomy assessment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=n5HblR27soE</t>
+    <t xml:space="preserve">Part 3: Primary varicose veins of the great saphenous vein. Saphenofemoral junction reflux test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=QFDDU7lpsuA</t>
   </si>
   <si>
     <t xml:space="preserve">V279</t>
   </si>
   <si>
-    <t xml:space="preserve">Part 3: Primary varicose veins of the great saphenous vein. Saphenofemoral junction reflux test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=QFDDU7lpsuA</t>
+    <t xml:space="preserve">Venous ultrasound course: Identifying varicose veins in the insufficiency study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=LcuG9zdK4tM</t>
   </si>
   <si>
     <t xml:space="preserve">V280</t>
   </si>
   <si>
-    <t xml:space="preserve">Vascular Imaging Webinar Series: DVT And Venous Insufficiency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=KLt-sO1G74A</t>
+    <t xml:space="preserve">How to Scan the Abdominal Aorta with Ultrasound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=fyegmq-hMhI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ishlab chiqaruvchi (GE HealthCare)</t>
   </si>
   <si>
     <t xml:space="preserve">V281</t>
   </si>
   <si>
-    <t xml:space="preserve">Abdominal Aortic Aneurysm (AAA): Ultrasound Scanning Technique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=IbSW2GCMsoQ</t>
+    <t xml:space="preserve">Examining the Inferior Vena Cava (IVC) with Point of Care Ultrasound (POCUS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=HFpPPCS1wAw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universitet (Stanford Medicine 25)</t>
   </si>
   <si>
     <t xml:space="preserve">V282</t>
   </si>
   <si>
-    <t xml:space="preserve">Point of Care Ultrasound of the Abdominal Aorta - AMBOSS Video</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=w8wc8-40F1E</t>
+    <t xml:space="preserve">03.15.02; 11.29.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Point of Care Ultrasound of the Inferior Vena Cava (IVC) - AMBOSS Video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=Flc8xS2foOU</t>
   </si>
   <si>
     <t xml:space="preserve">AMBOSS: Medical Knowledge Distilled</t>
@@ -6325,90 +6346,36 @@
     <t xml:space="preserve">V283</t>
   </si>
   <si>
-    <t xml:space="preserve">Point of Care Ultrasound of the Inferior Vena Cava (IVC) - AMBOSS Video</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=Flc8xS2foOU</t>
+    <t xml:space="preserve">Essentials in Liver Transplant: Vascular and Biliary Complications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=BnucQlkwEk4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icahn School of Medicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universitet (Icahn School of Medicine)</t>
   </si>
   <si>
     <t xml:space="preserve">V284</t>
   </si>
   <si>
-    <t xml:space="preserve">Ultrasound Vessel Mapping for Dialysis Access Planning (Eric Peden, MD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=EjXcrvJTmYw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kasalxona (Houston Methodist)</t>
+    <t xml:space="preserve">Orthotopic Liver Transplant Hepatic Artery and Portal Vein Complications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=jF22GbTfFS4</t>
   </si>
   <si>
     <t xml:space="preserve">V285</t>
   </si>
   <si>
-    <t xml:space="preserve">Vascular Imaging Webinar Series: Arteriovenous Mapping for Dialysis Access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=cFHfoL1k_pk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How to Scan Dialysis Fistulas -Ultrasound Tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=-8VG1bBhchI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V287</t>
-  </si>
-  <si>
     <t xml:space="preserve">Renal/Kidney Transplant Duplex Protocol</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.youtube.com/watch?v=KGFphcefwXA</t>
   </si>
   <si>
-    <t xml:space="preserve">V288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultrasound of Renal Transplant Vascular Complications: What to Know</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=eNsLjk2fJxc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertebral Arteries &amp; Subclavian Steal: Here's the Breakdown You Need by an Ultrasound Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=TeGAC9MoZow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Path2Passing </t>
-  </si>
-  <si>
-    <t xml:space="preserve">V290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doppler Imaging of Liver Transplants Diagnoses and Dilemmas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=3El9mtbhkX4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orthotopic Liver Transplant Hepatic Artery and Portal Vein Complications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=jF22GbTfFS4</t>
-  </si>
-  <si>
     <t xml:space="preserve">Qidiruvdagi ma’lumot</t>
   </si>
   <si>
@@ -6724,49 +6691,37 @@
     <t xml:space="preserve">24.1 da 3 ta dars yetarli</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=I4lJJs_eUGg</t>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=I4lJJs_eUGg</t>
   </si>
   <si>
     <t xml:space="preserve">Sonographic evaluation of the liver transplant - Lecture</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=hbVxhOV6NFw</t>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=hbVxhOV6NFw</t>
   </si>
   <si>
     <t xml:space="preserve">Vascular ultrasound made simple</t>
   </si>
   <si>
-    <t xml:space="preserve">25-bobda yetarli dars bor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=TeGAC9MoZow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertebral Arteries &amp; Subclavian Steal (Path2Passing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=_DiApj4D3jc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carotid Artery Color/Spectral Doppler Ultrasound Normal Vs Abnormal Images</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=KArjnqDxBE0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duplex ultrasound for Peripheral Artery Disease (Rama Surgery)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=-4tJgiWazjA</t>
+    <t xml:space="preserve">25.1 da 3 ta dars yetarli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=-4tJgiWazjA</t>
   </si>
   <si>
     <t xml:space="preserve">Saphenous Vein Doppler Ultrasound Normal Vs Abnormal</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=SHhKyEaW1NM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How To: Abdominal Ultrasound - Aorta Measurements (Sonosite)</t>
+    <t xml:space="preserve">25.6 da 3 ta dars yetarli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=tqt1Wr5-q-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplex Exam of Aorta and IVC - Case Study (MintMedical)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7 da 3 ta dars yetarli</t>
   </si>
   <si>
     <t xml:space="preserve">Kichik mavzular</t>
@@ -8701,7 +8656,7 @@
       </c>
       <c r="E29" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A29,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A29&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
@@ -8753,7 +8708,7 @@
       </c>
       <c r="E31" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A31,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A31&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
@@ -10254,7 +10209,7 @@
       </c>
       <c r="E90" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A90,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A90&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
@@ -10329,7 +10284,7 @@
       </c>
       <c r="E93" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A93,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A93&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6"/>
       <c r="G93" s="6" t="s">
@@ -10356,7 +10311,7 @@
       </c>
       <c r="E94" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A94,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A94&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6"/>
       <c r="G94" s="6" t="s">
@@ -12343,7 +12298,7 @@
       </c>
       <c r="E173" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A173,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A173&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
@@ -12393,7 +12348,7 @@
       </c>
       <c r="E175" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A175,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A175&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
@@ -12418,7 +12373,7 @@
       </c>
       <c r="E176" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A176,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A176&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
@@ -12443,7 +12398,7 @@
       </c>
       <c r="E177" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A177,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A177&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
@@ -12518,7 +12473,7 @@
       </c>
       <c r="E180" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A180,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A180&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F180" s="6"/>
       <c r="G180" s="6"/>
@@ -12543,7 +12498,7 @@
       </c>
       <c r="E181" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A181,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A181&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F181" s="6"/>
       <c r="G181" s="6"/>
@@ -13522,13 +13477,13 @@
       </c>
       <c r="E220" s="6" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A220,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A220&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220" s="6"/>
       <c r="G220" s="6"/>
       <c r="H220" s="6" t="str">
         <f aca="false">IF(G220&lt;&gt;"","Takroriy",IF(E220=0,"Yetishmaydi",IF(F220="ha","Qisman to‘ldirilgan","Mavjud, lekin tekshirilmagan")))</f>
-        <v>Yetishmaydi</v>
+        <v>Mavjud, lekin tekshirilmagan</v>
       </c>
       <c r="I220" s="6"/>
     </row>
@@ -16573,7 +16528,7 @@
         <v>431</v>
       </c>
       <c r="C108" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>651</v>
@@ -16613,7 +16568,7 @@
         <v>435</v>
       </c>
       <c r="C110" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>651</v>
@@ -16633,7 +16588,7 @@
         <v>437</v>
       </c>
       <c r="C111" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>651</v>
@@ -16653,7 +16608,7 @@
         <v>439</v>
       </c>
       <c r="C112" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>651</v>
@@ -16713,7 +16668,7 @@
         <v>445</v>
       </c>
       <c r="C115" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>651</v>
@@ -16733,7 +16688,7 @@
         <v>447</v>
       </c>
       <c r="C116" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>651</v>
@@ -17180,7 +17135,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y292"/>
+  <dimension ref="A1:Y286"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -34660,7 +34615,7 @@
       </c>
       <c r="Y270" s="12"/>
     </row>
-    <row r="271" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="6" t="s">
         <v>2049</v>
       </c>
@@ -34668,7 +34623,7 @@
         <v>428</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D271" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B271,Mundarija!$A:$A,0)),"kod topilmadi")</f>
@@ -34744,10 +34699,10 @@
         <v>2056</v>
       </c>
       <c r="G272" s="6" t="s">
-        <v>1534</v>
+        <v>2057</v>
       </c>
       <c r="H272" s="6" t="s">
-        <v>1592</v>
+        <v>2058</v>
       </c>
       <c r="I272" s="6" t="s">
         <v>812</v>
@@ -34762,7 +34717,7 @@
         <v>839</v>
       </c>
       <c r="M272" s="6" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="N272" s="12" t="s">
         <v>816</v>
@@ -34790,7 +34745,7 @@
     </row>
     <row r="273" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="6" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>432</v>
@@ -34801,16 +34756,16 @@
         <v>25.2. Karotid va vertebral arteriyalar.</v>
       </c>
       <c r="E273" s="6" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="F273" s="11" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="G273" s="6" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="H273" s="6" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="I273" s="6" t="s">
         <v>812</v>
@@ -34825,7 +34780,7 @@
         <v>1683</v>
       </c>
       <c r="M273" s="6" t="s">
-        <v>847</v>
+        <v>1648</v>
       </c>
       <c r="N273" s="12" t="s">
         <v>816</v>
@@ -34853,7 +34808,7 @@
     </row>
     <row r="274" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="6" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>434</v>
@@ -34864,16 +34819,16 @@
         <v>25.3. Aterosklerotik blyashkalar, stenoz va okklyuziya.</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="G274" s="6" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="H274" s="6" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="I274" s="6" t="s">
         <v>812</v>
@@ -34916,7 +34871,7 @@
     </row>
     <row r="275" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="6" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>434</v>
@@ -34927,10 +34882,10 @@
         <v>25.3. Aterosklerotik blyashkalar, stenoz va okklyuziya.</v>
       </c>
       <c r="E275" s="6" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="F275" s="11" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="G275" s="6" t="s">
         <v>2044</v>
@@ -34951,7 +34906,7 @@
         <v>839</v>
       </c>
       <c r="M275" s="6" t="s">
-        <v>847</v>
+        <v>826</v>
       </c>
       <c r="N275" s="12" t="s">
         <v>816</v>
@@ -34979,27 +34934,27 @@
     </row>
     <row r="276" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="6" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C276" s="6"/>
       <c r="D276" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B276,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.4. Yuqori va pastki ekstremita arteriyalari.</v>
+        <v>25.3. Aterosklerotik blyashkalar, stenoz va okklyuziya.</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="F276" s="11" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="G276" s="6" t="s">
-        <v>1563</v>
+        <v>2075</v>
       </c>
       <c r="H276" s="6" t="s">
-        <v>1115</v>
+        <v>2076</v>
       </c>
       <c r="I276" s="6" t="s">
         <v>812</v>
@@ -35042,27 +34997,29 @@
     </row>
     <row r="277" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="6" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="B277" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="C277" s="6"/>
+      <c r="C277" s="6" t="s">
+        <v>432</v>
+      </c>
       <c r="D277" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B277,Mundarija!$A:$A,0)),"kod topilmadi")</f>
         <v>25.4. Yuqori va pastki ekstremita arteriyalari.</v>
       </c>
       <c r="E277" s="6" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
       <c r="F277" s="11" t="s">
-        <v>2075</v>
+        <v>2079</v>
       </c>
       <c r="G277" s="6" t="s">
-        <v>822</v>
+        <v>2067</v>
       </c>
       <c r="H277" s="6" t="s">
-        <v>2037</v>
+        <v>2068</v>
       </c>
       <c r="I277" s="6" t="s">
         <v>812</v>
@@ -35074,10 +35031,10 @@
         <v>813</v>
       </c>
       <c r="L277" s="6" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="M277" s="6" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="N277" s="12" t="s">
         <v>816</v>
@@ -35105,29 +35062,27 @@
     </row>
     <row r="278" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="6" t="s">
-        <v>2076</v>
+        <v>2080</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="C278" s="6" t="s">
-        <v>428</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="C278" s="6"/>
       <c r="D278" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B278,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.4. Yuqori va pastki ekstremita arteriyalari.</v>
+        <v>25.6. Yuzaki venalar va varikoz.</v>
       </c>
       <c r="E278" s="6" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="F278" s="11" t="s">
-        <v>2078</v>
+        <v>2082</v>
       </c>
       <c r="G278" s="6" t="s">
-        <v>1158</v>
+        <v>2044</v>
       </c>
       <c r="H278" s="6" t="s">
-        <v>1777</v>
+        <v>2045</v>
       </c>
       <c r="I278" s="6" t="s">
         <v>812</v>
@@ -35142,7 +35097,7 @@
         <v>839</v>
       </c>
       <c r="M278" s="6" t="s">
-        <v>847</v>
+        <v>826</v>
       </c>
       <c r="N278" s="12" t="s">
         <v>816</v>
@@ -35170,7 +35125,7 @@
     </row>
     <row r="279" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="6" t="s">
-        <v>2079</v>
+        <v>2083</v>
       </c>
       <c r="B279" s="6" t="s">
         <v>440</v>
@@ -35181,10 +35136,10 @@
         <v>25.6. Yuzaki venalar va varikoz.</v>
       </c>
       <c r="E279" s="6" t="s">
-        <v>2080</v>
+        <v>2084</v>
       </c>
       <c r="F279" s="11" t="s">
-        <v>2081</v>
+        <v>2085</v>
       </c>
       <c r="G279" s="6" t="s">
         <v>2044</v>
@@ -35233,7 +35188,7 @@
     </row>
     <row r="280" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="6" t="s">
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="B280" s="6" t="s">
         <v>440</v>
@@ -35244,16 +35199,16 @@
         <v>25.6. Yuzaki venalar va varikoz.</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>2083</v>
+        <v>2087</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>2084</v>
+        <v>2088</v>
       </c>
       <c r="G280" s="6" t="s">
-        <v>2044</v>
+        <v>1158</v>
       </c>
       <c r="H280" s="6" t="s">
-        <v>2045</v>
+        <v>1777</v>
       </c>
       <c r="I280" s="6" t="s">
         <v>812</v>
@@ -35294,31 +35249,31 @@
       </c>
       <c r="Y280" s="12"/>
     </row>
-    <row r="281" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="6" t="s">
-        <v>2085</v>
+        <v>2089</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>438</v>
+        <v>251</v>
       </c>
       <c r="D281" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B281,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.6. Yuzaki venalar va varikoz.</v>
+        <v>25.7. Qorin aortasi va pastki kava vena.</v>
       </c>
       <c r="E281" s="6" t="s">
-        <v>2086</v>
+        <v>2090</v>
       </c>
       <c r="F281" s="11" t="s">
-        <v>2087</v>
+        <v>2091</v>
       </c>
       <c r="G281" s="6" t="s">
-        <v>2052</v>
+        <v>1294</v>
       </c>
       <c r="H281" s="6" t="s">
-        <v>2053</v>
+        <v>2092</v>
       </c>
       <c r="I281" s="6" t="s">
         <v>812</v>
@@ -35330,10 +35285,10 @@
         <v>813</v>
       </c>
       <c r="L281" s="6" t="s">
-        <v>839</v>
+        <v>814</v>
       </c>
       <c r="M281" s="6" t="s">
-        <v>847</v>
+        <v>826</v>
       </c>
       <c r="N281" s="12" t="s">
         <v>816</v>
@@ -35361,29 +35316,29 @@
     </row>
     <row r="282" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="6" t="s">
-        <v>2088</v>
+        <v>2093</v>
       </c>
       <c r="B282" s="6" t="s">
         <v>442</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D282" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B282,Mundarija!$A:$A,0)),"kod topilmadi")</f>
         <v>25.7. Qorin aortasi va pastki kava vena.</v>
       </c>
       <c r="E282" s="6" t="s">
-        <v>2089</v>
+        <v>2094</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>2090</v>
+        <v>2095</v>
       </c>
       <c r="G282" s="6" t="s">
-        <v>1253</v>
+        <v>1652</v>
       </c>
       <c r="H282" s="6" t="s">
-        <v>1575</v>
+        <v>2096</v>
       </c>
       <c r="I282" s="6" t="s">
         <v>812</v>
@@ -35426,29 +35381,29 @@
     </row>
     <row r="283" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="6" t="s">
-        <v>2091</v>
+        <v>2097</v>
       </c>
       <c r="B283" s="6" t="s">
         <v>442</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>251</v>
+        <v>2098</v>
       </c>
       <c r="D283" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B283,Mundarija!$A:$A,0)),"kod topilmadi")</f>
         <v>25.7. Qorin aortasi va pastki kava vena.</v>
       </c>
       <c r="E283" s="6" t="s">
-        <v>2092</v>
+        <v>2099</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>2093</v>
+        <v>2100</v>
       </c>
       <c r="G283" s="6" t="s">
-        <v>2094</v>
+        <v>2101</v>
       </c>
       <c r="H283" s="6" t="s">
-        <v>2095</v>
+        <v>2102</v>
       </c>
       <c r="I283" s="6" t="s">
         <v>812</v>
@@ -35491,29 +35446,29 @@
     </row>
     <row r="284" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="6" t="s">
-        <v>2096</v>
+        <v>2103</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>442</v>
+        <v>190</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>255</v>
+        <v>446</v>
       </c>
       <c r="D284" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B284,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.7. Qorin aortasi va pastki kava vena.</v>
+        <v>10.8. Jigar transplantatini tekshirish.</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>2097</v>
+        <v>2104</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>2098</v>
+        <v>2105</v>
       </c>
       <c r="G284" s="6" t="s">
-        <v>2094</v>
+        <v>2106</v>
       </c>
       <c r="H284" s="6" t="s">
-        <v>2095</v>
+        <v>2107</v>
       </c>
       <c r="I284" s="6" t="s">
         <v>812</v>
@@ -35525,10 +35480,10 @@
         <v>813</v>
       </c>
       <c r="L284" s="6" t="s">
-        <v>814</v>
+        <v>1683</v>
       </c>
       <c r="M284" s="6" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="N284" s="12" t="s">
         <v>816</v>
@@ -35556,27 +35511,29 @@
     </row>
     <row r="285" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="6" t="s">
-        <v>2099</v>
+        <v>2108</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="C285" s="6"/>
+        <v>190</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>446</v>
+      </c>
       <c r="D285" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B285,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.8. Gemodializ arteriovenoz kirish yo‘llari.</v>
+        <v>10.8. Jigar transplantatini tekshirish.</v>
       </c>
       <c r="E285" s="6" t="s">
-        <v>2100</v>
+        <v>2109</v>
       </c>
       <c r="F285" s="11" t="s">
-        <v>2101</v>
+        <v>2110</v>
       </c>
       <c r="G285" s="6" t="s">
-        <v>1344</v>
+        <v>1170</v>
       </c>
       <c r="H285" s="6" t="s">
-        <v>2102</v>
+        <v>845</v>
       </c>
       <c r="I285" s="6" t="s">
         <v>812</v>
@@ -35591,7 +35548,7 @@
         <v>1683</v>
       </c>
       <c r="M285" s="6" t="s">
-        <v>847</v>
+        <v>1648</v>
       </c>
       <c r="N285" s="12" t="s">
         <v>816</v>
@@ -35617,29 +35574,31 @@
       </c>
       <c r="Y285" s="12"/>
     </row>
-    <row r="286" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="6" t="s">
-        <v>2103</v>
+        <v>2111</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="C286" s="6"/>
+        <v>446</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>245</v>
+      </c>
       <c r="D286" s="6" t="str">
         <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B286,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.8. Gemodializ arteriovenoz kirish yo‘llari.</v>
+        <v>25.9. Transplantat tomirlari.</v>
       </c>
       <c r="E286" s="6" t="s">
-        <v>2104</v>
+        <v>2112</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>2105</v>
+        <v>2113</v>
       </c>
       <c r="G286" s="6" t="s">
-        <v>2052</v>
+        <v>822</v>
       </c>
       <c r="H286" s="6" t="s">
-        <v>2053</v>
+        <v>2037</v>
       </c>
       <c r="I286" s="6" t="s">
         <v>812</v>
@@ -35654,7 +35613,7 @@
         <v>839</v>
       </c>
       <c r="M286" s="6" t="s">
-        <v>847</v>
+        <v>826</v>
       </c>
       <c r="N286" s="12" t="s">
         <v>816</v>
@@ -35680,396 +35639,10 @@
       </c>
       <c r="Y286" s="12"/>
     </row>
-    <row r="287" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="6" t="s">
-        <v>2106</v>
-      </c>
-      <c r="B287" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="C287" s="6"/>
-      <c r="D287" s="6" t="str">
-        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B287,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.8. Gemodializ arteriovenoz kirish yo‘llari.</v>
-      </c>
-      <c r="E287" s="6" t="s">
-        <v>2107</v>
-      </c>
-      <c r="F287" s="11" t="s">
-        <v>2108</v>
-      </c>
-      <c r="G287" s="6" t="s">
-        <v>1601</v>
-      </c>
-      <c r="H287" s="6" t="s">
-        <v>1602</v>
-      </c>
-      <c r="I287" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="J287" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="K287" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="L287" s="6" t="s">
-        <v>839</v>
-      </c>
-      <c r="M287" s="6" t="s">
-        <v>826</v>
-      </c>
-      <c r="N287" s="12" t="s">
-        <v>816</v>
-      </c>
-      <c r="O287" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="P287" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q287" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R287" s="12"/>
-      <c r="S287" s="12"/>
-      <c r="T287" s="12"/>
-      <c r="U287" s="12"/>
-      <c r="V287" s="12"/>
-      <c r="W287" s="12"/>
-      <c r="X287" s="6" t="str">
-        <f aca="false">IF(COUNT(R287:W287)=6,SUM(R287:W287),"ko‘rilmagan")</f>
-        <v>ko‘rilmagan</v>
-      </c>
-      <c r="Y287" s="12"/>
-    </row>
-    <row r="288" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="6" t="s">
-        <v>2109</v>
-      </c>
-      <c r="B288" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="C288" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D288" s="6" t="str">
-        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B288,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.9. Transplantat tomirlari.</v>
-      </c>
-      <c r="E288" s="6" t="s">
-        <v>2110</v>
-      </c>
-      <c r="F288" s="11" t="s">
-        <v>2111</v>
-      </c>
-      <c r="G288" s="6" t="s">
-        <v>822</v>
-      </c>
-      <c r="H288" s="6" t="s">
-        <v>2037</v>
-      </c>
-      <c r="I288" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="J288" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="K288" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="L288" s="6" t="s">
-        <v>839</v>
-      </c>
-      <c r="M288" s="6" t="s">
-        <v>826</v>
-      </c>
-      <c r="N288" s="12" t="s">
-        <v>816</v>
-      </c>
-      <c r="O288" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="P288" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q288" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R288" s="12"/>
-      <c r="S288" s="12"/>
-      <c r="T288" s="12"/>
-      <c r="U288" s="12"/>
-      <c r="V288" s="12"/>
-      <c r="W288" s="12"/>
-      <c r="X288" s="6" t="str">
-        <f aca="false">IF(COUNT(R288:W288)=6,SUM(R288:W288),"ko‘rilmagan")</f>
-        <v>ko‘rilmagan</v>
-      </c>
-      <c r="Y288" s="12"/>
-    </row>
-    <row r="289" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="6" t="s">
-        <v>2112</v>
-      </c>
-      <c r="B289" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="C289" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D289" s="6" t="str">
-        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B289,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.9. Transplantat tomirlari.</v>
-      </c>
-      <c r="E289" s="6" t="s">
-        <v>2113</v>
-      </c>
-      <c r="F289" s="11" t="s">
-        <v>2114</v>
-      </c>
-      <c r="G289" s="6" t="s">
-        <v>844</v>
-      </c>
-      <c r="H289" s="6" t="s">
-        <v>1784</v>
-      </c>
-      <c r="I289" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="J289" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="K289" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="L289" s="6" t="s">
-        <v>1683</v>
-      </c>
-      <c r="M289" s="6" t="s">
-        <v>847</v>
-      </c>
-      <c r="N289" s="12" t="s">
-        <v>816</v>
-      </c>
-      <c r="O289" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="P289" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q289" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R289" s="12"/>
-      <c r="S289" s="12"/>
-      <c r="T289" s="12"/>
-      <c r="U289" s="12"/>
-      <c r="V289" s="12"/>
-      <c r="W289" s="12"/>
-      <c r="X289" s="6" t="str">
-        <f aca="false">IF(COUNT(R289:W289)=6,SUM(R289:W289),"ko‘rilmagan")</f>
-        <v>ko‘rilmagan</v>
-      </c>
-      <c r="Y289" s="12"/>
-    </row>
-    <row r="290" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="6" t="s">
-        <v>2115</v>
-      </c>
-      <c r="B290" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="C290" s="6"/>
-      <c r="D290" s="6" t="str">
-        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B290,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.2. Karotid va vertebral arteriyalar.</v>
-      </c>
-      <c r="E290" s="6" t="s">
-        <v>2116</v>
-      </c>
-      <c r="F290" s="11" t="s">
-        <v>2117</v>
-      </c>
-      <c r="G290" s="6" t="s">
-        <v>2118</v>
-      </c>
-      <c r="H290" s="6" t="s">
-        <v>823</v>
-      </c>
-      <c r="I290" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="J290" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="K290" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="L290" s="6" t="s">
-        <v>839</v>
-      </c>
-      <c r="M290" s="6" t="s">
-        <v>847</v>
-      </c>
-      <c r="N290" s="12" t="s">
-        <v>816</v>
-      </c>
-      <c r="O290" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="P290" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q290" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R290" s="12"/>
-      <c r="S290" s="12"/>
-      <c r="T290" s="12"/>
-      <c r="U290" s="12"/>
-      <c r="V290" s="12"/>
-      <c r="W290" s="12"/>
-      <c r="X290" s="6" t="str">
-        <f aca="false">IF(COUNT(R290:W290)=6,SUM(R290:W290),"ko‘rilmagan")</f>
-        <v>ko‘rilmagan</v>
-      </c>
-      <c r="Y290" s="12"/>
-    </row>
-    <row r="291" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="6" t="s">
-        <v>2119</v>
-      </c>
-      <c r="B291" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="C291" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D291" s="6" t="str">
-        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B291,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>25.9. Transplantat tomirlari.</v>
-      </c>
-      <c r="E291" s="6" t="s">
-        <v>2120</v>
-      </c>
-      <c r="F291" s="11" t="s">
-        <v>2121</v>
-      </c>
-      <c r="G291" s="6" t="s">
-        <v>1170</v>
-      </c>
-      <c r="H291" s="6" t="s">
-        <v>845</v>
-      </c>
-      <c r="I291" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="J291" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="K291" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="L291" s="6" t="s">
-        <v>1683</v>
-      </c>
-      <c r="M291" s="6" t="s">
-        <v>847</v>
-      </c>
-      <c r="N291" s="12" t="s">
-        <v>816</v>
-      </c>
-      <c r="O291" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="P291" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q291" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R291" s="12"/>
-      <c r="S291" s="12"/>
-      <c r="T291" s="12"/>
-      <c r="U291" s="12"/>
-      <c r="V291" s="12"/>
-      <c r="W291" s="12"/>
-      <c r="X291" s="6" t="str">
-        <f aca="false">IF(COUNT(R291:W291)=6,SUM(R291:W291),"ko‘rilmagan")</f>
-        <v>ko‘rilmagan</v>
-      </c>
-      <c r="Y291" s="12"/>
-    </row>
-    <row r="292" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="6" t="s">
-        <v>2122</v>
-      </c>
-      <c r="B292" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="C292" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="D292" s="6" t="str">
-        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B292,Mundarija!$A:$A,0)),"kod topilmadi")</f>
-        <v>10.8. Jigar transplantatini tekshirish.</v>
-      </c>
-      <c r="E292" s="6" t="s">
-        <v>2123</v>
-      </c>
-      <c r="F292" s="11" t="s">
-        <v>2124</v>
-      </c>
-      <c r="G292" s="6" t="s">
-        <v>1170</v>
-      </c>
-      <c r="H292" s="6" t="s">
-        <v>845</v>
-      </c>
-      <c r="I292" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="J292" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="K292" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="L292" s="6" t="s">
-        <v>1683</v>
-      </c>
-      <c r="M292" s="6" t="s">
-        <v>847</v>
-      </c>
-      <c r="N292" s="12" t="s">
-        <v>816</v>
-      </c>
-      <c r="O292" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="P292" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q292" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R292" s="12"/>
-      <c r="S292" s="12"/>
-      <c r="T292" s="12"/>
-      <c r="U292" s="12"/>
-      <c r="V292" s="12"/>
-      <c r="W292" s="12"/>
-      <c r="X292" s="6" t="str">
-        <f aca="false">IF(COUNT(R292:W292)=6,SUM(R292:W292),"ko‘rilmagan")</f>
-        <v>ko‘rilmagan</v>
-      </c>
-      <c r="Y292" s="12"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Y292"/>
+  <autoFilter ref="A1:Y286"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="0 dan 5 gacha butun son" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:W492" type="whole">
+    <dataValidation allowBlank="true" error="0 dan 5 gacha butun son" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:W486" type="whole">
       <formula1>0</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -36345,27 +35918,21 @@
     <hyperlink ref="F269" r:id="rId268" display="https://www.youtube.com/watch?v=ihXKv9qqbZw"/>
     <hyperlink ref="F270" r:id="rId269" display="https://www.youtube.com/watch?v=IaejYqKM6mI"/>
     <hyperlink ref="F271" r:id="rId270" display="https://www.youtube.com/watch?v=X739XUv0xkE"/>
-    <hyperlink ref="F272" r:id="rId271" display="https://www.youtube.com/watch?v=_CAkI846j7E"/>
+    <hyperlink ref="F272" r:id="rId271" display="https://www.youtube.com/watch?v=TeGAC9MoZow"/>
     <hyperlink ref="F273" r:id="rId272" display="https://www.youtube.com/watch?v=dRVXK3DjBzk"/>
     <hyperlink ref="F274" r:id="rId273" display="https://www.youtube.com/watch?v=pXjCmheNuug"/>
     <hyperlink ref="F275" r:id="rId274" display="https://www.youtube.com/watch?v=76hyW1-XkGk"/>
-    <hyperlink ref="F276" r:id="rId275" display="https://www.youtube.com/watch?v=4JyRA2xSQ6o"/>
-    <hyperlink ref="F277" r:id="rId276" display="https://www.youtube.com/watch?v=J4z7BCopSvs"/>
-    <hyperlink ref="F278" r:id="rId277" display="https://www.youtube.com/watch?v=Vf7nE0vBSco"/>
-    <hyperlink ref="F279" r:id="rId278" display="https://www.youtube.com/watch?v=n5HblR27soE"/>
-    <hyperlink ref="F280" r:id="rId279" display="https://www.youtube.com/watch?v=QFDDU7lpsuA"/>
-    <hyperlink ref="F281" r:id="rId280" display="https://www.youtube.com/watch?v=KLt-sO1G74A"/>
-    <hyperlink ref="F282" r:id="rId281" display="https://www.youtube.com/watch?v=IbSW2GCMsoQ"/>
-    <hyperlink ref="F283" r:id="rId282" display="https://www.youtube.com/watch?v=w8wc8-40F1E"/>
-    <hyperlink ref="F284" r:id="rId283" display="https://www.youtube.com/watch?v=Flc8xS2foOU"/>
-    <hyperlink ref="F285" r:id="rId284" display="https://www.youtube.com/watch?v=EjXcrvJTmYw"/>
-    <hyperlink ref="F286" r:id="rId285" display="https://www.youtube.com/watch?v=cFHfoL1k_pk"/>
-    <hyperlink ref="F287" r:id="rId286" display="https://www.youtube.com/watch?v=-8VG1bBhchI"/>
-    <hyperlink ref="F288" r:id="rId287" display="https://www.youtube.com/watch?v=KGFphcefwXA"/>
-    <hyperlink ref="F289" r:id="rId288" display="https://www.youtube.com/watch?v=eNsLjk2fJxc"/>
-    <hyperlink ref="F290" r:id="rId289" display="https://www.youtube.com/watch?v=TeGAC9MoZow"/>
-    <hyperlink ref="F291" r:id="rId290" display="https://www.youtube.com/watch?v=3El9mtbhkX4"/>
-    <hyperlink ref="F292" r:id="rId291" display="https://www.youtube.com/watch?v=jF22GbTfFS4"/>
+    <hyperlink ref="F276" r:id="rId275" display="https://www.youtube.com/watch?v=fC7gjgVx0LI"/>
+    <hyperlink ref="F277" r:id="rId276" display="https://www.youtube.com/watch?v=VYhlgQu-JOI"/>
+    <hyperlink ref="F278" r:id="rId277" display="https://www.youtube.com/watch?v=n5HblR27soE"/>
+    <hyperlink ref="F279" r:id="rId278" display="https://www.youtube.com/watch?v=QFDDU7lpsuA"/>
+    <hyperlink ref="F280" r:id="rId279" display="https://www.youtube.com/watch?v=LcuG9zdK4tM"/>
+    <hyperlink ref="F281" r:id="rId280" display="https://www.youtube.com/watch?v=fyegmq-hMhI"/>
+    <hyperlink ref="F282" r:id="rId281" display="https://www.youtube.com/watch?v=HFpPPCS1wAw"/>
+    <hyperlink ref="F283" r:id="rId282" display="https://www.youtube.com/watch?v=Flc8xS2foOU"/>
+    <hyperlink ref="F284" r:id="rId283" display="https://www.youtube.com/watch?v=BnucQlkwEk4"/>
+    <hyperlink ref="F285" r:id="rId284" display="https://www.youtube.com/watch?v=jF22GbTfFS4"/>
+    <hyperlink ref="F286" r:id="rId285" display="https://www.youtube.com/watch?v=KGFphcefwXA"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -36374,7 +35941,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId292"/>
+  <drawing r:id="rId286"/>
 </worksheet>
 </file>
 
@@ -36383,7 +35950,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -36396,195 +35963,195 @@
         <v>746</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>2125</v>
+        <v>2114</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2126</v>
+        <v>2115</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2127</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>2128</v>
+        <v>2117</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2129</v>
+        <v>2118</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2130</v>
+        <v>2119</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2131</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>2132</v>
+        <v>2121</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2133</v>
+        <v>2122</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>2134</v>
+        <v>2123</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>2131</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>2135</v>
+        <v>2124</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2136</v>
+        <v>2125</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>2137</v>
+        <v>2126</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>2131</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>2138</v>
+        <v>2127</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2139</v>
+        <v>2128</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>2140</v>
+        <v>2129</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>2131</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>2141</v>
+        <v>2130</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2142</v>
+        <v>2131</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>2143</v>
+        <v>2132</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2144</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>2145</v>
+        <v>2134</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>2146</v>
+        <v>2135</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>2147</v>
+        <v>2136</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>2149</v>
+        <v>2138</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>2150</v>
+        <v>2139</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>2151</v>
+        <v>2140</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>2152</v>
+        <v>2141</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>2153</v>
+        <v>2142</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>2154</v>
+        <v>2143</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>2156</v>
+        <v>2145</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>2157</v>
+        <v>2146</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>2158</v>
+        <v>2147</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>2159</v>
+        <v>2148</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>2160</v>
+        <v>2149</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>2161</v>
+        <v>2150</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>2162</v>
+        <v>2151</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>2163</v>
+        <v>2152</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>2164</v>
+        <v>2153</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>2144</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>2165</v>
+        <v>2154</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>2166</v>
+        <v>2155</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>2167</v>
+        <v>2156</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>2168</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>2169</v>
+        <v>2158</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>2170</v>
+        <v>2159</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>2171</v>
+        <v>2160</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36595,10 +36162,10 @@
         <v>962</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>2172</v>
+        <v>2161</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>2173</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36609,10 +36176,10 @@
         <v>1054</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>2172</v>
+        <v>2161</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>2173</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36623,430 +36190,388 @@
         <v>1060</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>2172</v>
+        <v>2161</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>2173</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>2174</v>
+        <v>2163</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>2175</v>
+        <v>2164</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>2154</v>
+        <v>2143</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>2176</v>
+        <v>2165</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>2177</v>
+        <v>2166</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>2158</v>
+        <v>2147</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>2178</v>
+        <v>2167</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>2179</v>
+        <v>2168</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>2180</v>
+        <v>2169</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>2181</v>
+        <v>2170</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>2182</v>
+        <v>2171</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>2183</v>
+        <v>2172</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>2184</v>
+        <v>2173</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>2185</v>
+        <v>2174</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>2186</v>
+        <v>2175</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>2187</v>
+        <v>2176</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>2188</v>
+        <v>2177</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>2186</v>
+        <v>2175</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>2189</v>
+        <v>2178</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>2190</v>
+        <v>2179</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>2186</v>
+        <v>2175</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>2191</v>
+        <v>2180</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>2192</v>
+        <v>2181</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>2193</v>
+        <v>2182</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>2194</v>
+        <v>2183</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>2195</v>
+        <v>2184</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>2196</v>
+        <v>2185</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>2197</v>
+        <v>2186</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>2198</v>
+        <v>2187</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>2199</v>
+        <v>2188</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>2200</v>
+        <v>2189</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>2201</v>
+        <v>2190</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>2202</v>
+        <v>2191</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>2203</v>
+        <v>2192</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>2204</v>
+        <v>2193</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>2205</v>
+        <v>2194</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>2206</v>
+        <v>2195</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>2207</v>
+        <v>2196</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>2193</v>
+        <v>2182</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>2208</v>
+        <v>2197</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>2209</v>
+        <v>2198</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>2186</v>
+        <v>2175</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>2210</v>
+        <v>2199</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>2211</v>
+        <v>2200</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>2186</v>
+        <v>2175</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>2212</v>
+        <v>2201</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>2213</v>
+        <v>2202</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>2193</v>
+        <v>2182</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>2214</v>
+        <v>2203</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>2215</v>
+        <v>2204</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>2186</v>
+        <v>2175</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>2216</v>
+        <v>2205</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>2217</v>
+        <v>2206</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>2193</v>
+        <v>2182</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>2218</v>
+        <v>2207</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>2219</v>
+        <v>2208</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>2193</v>
+        <v>2182</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>2220</v>
+        <v>2209</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>2221</v>
+        <v>2210</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>2193</v>
+        <v>2182</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>2222</v>
+        <v>2211</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>2223</v>
+        <v>2212</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>2196</v>
+        <v>2185</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>2224</v>
+        <v>2213</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>2225</v>
+        <v>2214</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>2226</v>
+        <v>2215</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>2227</v>
+        <v>2216</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>2228</v>
+        <v>2217</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>2229</v>
+        <v>2218</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>2230</v>
+        <v>2219</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>2231</v>
+        <v>2220</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>2186</v>
+        <v>2175</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>2232</v>
+        <v>2221</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>2233</v>
+        <v>2222</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>2234</v>
+        <v>2223</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>2235</v>
+        <v>2224</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>2236</v>
+        <v>2225</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>2234</v>
+        <v>2226</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>2148</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>2237</v>
+        <v>2227</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>2238</v>
+        <v>2228</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>2234</v>
+        <v>2229</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>2148</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
-        <v>2239</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2240</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>2148</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11" t="s">
-        <v>2241</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2242</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>2148</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="11" t="s">
-        <v>2243</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2244</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
     </row>
   </sheetData>
@@ -37090,13 +36615,10 @@
     <hyperlink ref="A38" r:id="rId37" display="https://www.youtube.com/watch?v=NXdmwnSjhx8"/>
     <hyperlink ref="A39" r:id="rId38" display="https://www.youtube.com/watch?v=UtgJ85-OdHM"/>
     <hyperlink ref="A40" r:id="rId39" display="https://www.youtube.com/watch?v=poGrtzLVDLk"/>
-    <hyperlink ref="A41" r:id="rId40" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=I4lJJs_eUGg"/>
-    <hyperlink ref="A42" r:id="rId41" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=hbVxhOV6NFw"/>
-    <hyperlink ref="A43" r:id="rId42" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=TeGAC9MoZow"/>
-    <hyperlink ref="A44" r:id="rId43" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=_DiApj4D3jc"/>
-    <hyperlink ref="A45" r:id="rId44" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=KArjnqDxBE0"/>
-    <hyperlink ref="A46" r:id="rId45" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=-4tJgiWazjA"/>
-    <hyperlink ref="A47" r:id="rId46" display="https://www.youtube.com/watch?v=https://www.youtube.com/watch?v=SHhKyEaW1NM"/>
+    <hyperlink ref="A41" r:id="rId40" display="https://www.youtube.com/watch?v=I4lJJs_eUGg"/>
+    <hyperlink ref="A42" r:id="rId41" display="https://www.youtube.com/watch?v=hbVxhOV6NFw"/>
+    <hyperlink ref="A43" r:id="rId42" display="https://www.youtube.com/watch?v=-4tJgiWazjA"/>
+    <hyperlink ref="A44" r:id="rId43" display="https://www.youtube.com/watch?v=tqt1Wr5-q-E"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -37132,22 +36654,22 @@
         <v>36</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2245</v>
+        <v>2230</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2246</v>
+        <v>2231</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>2247</v>
+        <v>2232</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2248</v>
+        <v>2233</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2249</v>
+        <v>2234</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>2168</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38059,15 +37581,15 @@
       </c>
       <c r="D30" s="6" t="n">
         <f aca="false">COUNTIFS(Mundarija!$C$2:$C$254,B30,Mundarija!$E$2:$E$254,"&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="15" t="n">
         <f aca="false">IF(C30=0,0,D30/C30)</f>
-        <v>0</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="F30" s="6" t="n">
         <f aca="false">COUNTIFS(Mundarija!$C$2:$C$254,B30,Mundarija!$H$2:$H$254,"Yetishmaydi")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G30" s="6" t="n">
         <f aca="false">COUNTIFS(Mundarija!$C$2:$C$254,B30,Mundarija!$H$2:$H$254,"Qisman to‘ldirilgan")</f>
@@ -38209,7 +37731,7 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="16"/>
       <c r="B35" s="16" t="s">
-        <v>2250</v>
+        <v>2235</v>
       </c>
       <c r="C35" s="16" t="n">
         <f aca="false">SUM(C2:C34)</f>
@@ -38217,15 +37739,15 @@
       </c>
       <c r="D35" s="16" t="n">
         <f aca="false">SUM(D2:D34)</f>
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E35" s="17" t="n">
         <f aca="false">IF(C35=0,0,D35/C35)</f>
-        <v>0.703557312252965</v>
+        <v>0.707509881422925</v>
       </c>
       <c r="F35" s="16" t="n">
         <f aca="false">SUM(F2:F34)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G35" s="16" t="n">
         <f aca="false">SUM(G2:G34)</f>
@@ -38238,26 +37760,26 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>2251</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>2252</v>
+        <v>2237</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>2253</v>
+        <v>2238</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>2254</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>2255</v>
+        <v>2240</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>2256</v>
+        <v>2241</v>
       </c>
       <c r="C39" s="15" t="n">
         <f aca="false">C35/253</f>
@@ -38266,22 +37788,22 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>2257</v>
+        <v>2242</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>2258</v>
+        <v>2243</v>
       </c>
       <c r="C40" s="15" t="n">
         <f aca="false">E35</f>
-        <v>0.703557312252965</v>
+        <v>0.707509881422925</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>2259</v>
+        <v>2244</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>2260</v>
+        <v>2245</v>
       </c>
       <c r="C41" s="15" t="n">
         <f aca="false">SUM(D2:D7)/SUM(C2:C7)</f>
@@ -38290,25 +37812,25 @@
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>2261</v>
+        <v>2246</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>2262</v>
+        <v>2247</v>
       </c>
       <c r="C42" s="15" t="n">
-        <f aca="false">(COUNTIF(Katalog!$Q$2:$Q$292,"Havola tekshirilgan*")+COUNTIF(Katalog!$Q$2:$Q$292,"Metadata tekshirilgan*"))/COUNTA(Katalog!$A$2:$A$292)</f>
-        <v>0.989690721649485</v>
+        <f aca="false">(COUNTIF(Katalog!$Q$2:$Q$286,"Havola tekshirilgan*")+COUNTIF(Katalog!$Q$2:$Q$286,"Metadata tekshirilgan*"))/COUNTA(Katalog!$A$2:$A$286)</f>
+        <v>0.989473684210526</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>2263</v>
+        <v>2248</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>2264</v>
+        <v>2249</v>
       </c>
       <c r="C43" s="15" t="n">
-        <f aca="false">COUNT(Katalog!$X$2:$X$292)/COUNTA(Katalog!$A$2:$A$292)</f>
+        <f aca="false">COUNT(Katalog!$X$2:$X$286)/COUNTA(Katalog!$A$2:$A$286)</f>
         <v>0</v>
       </c>
     </row>
@@ -38340,400 +37862,400 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>2265</v>
+        <v>2250</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>2266</v>
+        <v>2251</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2267</v>
+        <v>2252</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>2268</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>2269</v>
+        <v>2254</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2270</v>
+        <v>2255</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2271</v>
+        <v>2256</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>2272</v>
+        <v>2257</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>2273</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2274</v>
+        <v>2259</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2275</v>
+        <v>2260</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>2276</v>
+        <v>2261</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>2277</v>
+        <v>2262</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>2278</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2279</v>
+        <v>2264</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2280</v>
+        <v>2265</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>2281</v>
+        <v>2266</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>2282</v>
+        <v>2267</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>2283</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2284</v>
+        <v>2269</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2285</v>
+        <v>2270</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>2286</v>
+        <v>2271</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>2282</v>
+        <v>2267</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>2287</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2288</v>
+        <v>2273</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2289</v>
+        <v>2274</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>2290</v>
+        <v>2275</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2282</v>
+        <v>2267</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>2291</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2292</v>
+        <v>2277</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>2293</v>
+        <v>2278</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>2282</v>
+        <v>2267</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>2295</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>2296</v>
+        <v>2281</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>2297</v>
+        <v>2282</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>2298</v>
+        <v>2283</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>2299</v>
+        <v>2284</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>2300</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2301</v>
+        <v>2286</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>2302</v>
+        <v>2287</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>2303</v>
+        <v>2288</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2304</v>
+        <v>2289</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>2305</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>2306</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>2307</v>
+        <v>2292</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>2308</v>
+        <v>2293</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>2126</v>
+        <v>2115</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>2309</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>2310</v>
+        <v>2295</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>2311</v>
+        <v>2296</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>2312</v>
+        <v>2297</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>2313</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>2310</v>
+        <v>2295</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>2314</v>
+        <v>2299</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>2315</v>
+        <v>2300</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>2316</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>2310</v>
+        <v>2295</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>2317</v>
+        <v>2302</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>2318</v>
+        <v>2303</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>2319</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>2310</v>
+        <v>2295</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>2320</v>
+        <v>2305</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>2321</v>
+        <v>2306</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>2322</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>2308</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>2310</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>2323</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>2324</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>2325</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>2310</v>
+        <v>2295</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>2326</v>
+        <v>2311</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>2327</v>
+        <v>2312</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>2328</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>2329</v>
+        <v>2314</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>95</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>2330</v>
+        <v>2315</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>2331</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>2332</v>
+        <v>2317</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>63</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>2333</v>
+        <v>2318</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>2334</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>2332</v>
+        <v>2317</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>2335</v>
+        <v>2320</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>2336</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>2332</v>
+        <v>2317</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>2337</v>
+        <v>2322</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>2338</v>
+        <v>2323</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>2339</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>2332</v>
+        <v>2317</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>2340</v>
+        <v>2325</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>2341</v>
+        <v>2326</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>2342</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>2248</v>
+        <v>2233</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>2343</v>
+        <v>2328</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>2344</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>2248</v>
+        <v>2233</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>201</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>2345</v>
+        <v>2330</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>2346</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>2248</v>
+        <v>2233</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>354</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>2347</v>
+        <v>2332</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>2348</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>2349</v>
+        <v>2334</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>482</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>2350</v>
+        <v>2335</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>2351</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>2352</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>2353</v>
+        <v>2338</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>2354</v>
+        <v>2339</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>2355</v>
+        <v>2340</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>41</v>
@@ -38741,86 +38263,86 @@
     </row>
     <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>2356</v>
+        <v>2341</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>2357</v>
+        <v>2342</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>2358</v>
+        <v>2343</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>2359</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>2360</v>
+        <v>2345</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>2361</v>
+        <v>2346</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>2362</v>
+        <v>2347</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>2359</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>2363</v>
+        <v>2348</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>2364</v>
+        <v>2349</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>2365</v>
+        <v>2350</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>2366</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>2367</v>
+        <v>2352</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>2368</v>
+        <v>2353</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>2369</v>
+        <v>2354</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>2370</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>2371</v>
+        <v>2356</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>2372</v>
+        <v>2357</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>2373</v>
+        <v>2358</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>2374</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>2375</v>
+        <v>2360</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>2376</v>
+        <v>2361</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>2377</v>
+        <v>2362</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>2378</v>
+        <v>2363</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
+++ b/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Audit" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Katalog!$A$1:$Y$298</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Katalog!$A$1:$Y$305</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Mundarija!$A$1:$I$254</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Qidiruv navbati'!$A$1:$F$117</definedName>
   </definedNames>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6909" uniqueCount="2404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7023" uniqueCount="2430">
   <si>
     <t xml:space="preserve">SHOKALON — videodarslar katalogi, 7-versiya</t>
   </si>
@@ -6482,6 +6482,84 @@
   </si>
   <si>
     <t xml:space="preserve">Universitet (Icahn School of Medicine)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subclavian Artery Doppler Ultrasound Normal Vs Abnormal Images | Stenosis &amp; Steal Syndrome USG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=sOwTdJPSBeI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel sessiyadan qo‘shildi (2026-10-17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vascular ultrasound free lectures: carotid and venous ultrasound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=fWYo00L5w6o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venous ultrasound course: Deciphering DVT waveforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=zFtlbk2yzn8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultrasound and Venous Insufficiency (Ulises Baltazar, MD and William Marston, MD) October 28, 2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=JwIWZuq5o14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universitet kasalxonasi (Houston Methodist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POCUS: Differentiating the Aorta and IVC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=QaQNYFjvKxs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POCUS Certification Academy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ta’lim kanali (POCUS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doppler Ultrasound of the Liver and Portal Hypertension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=R_BbuhzjQzc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hepatic Doppler Made Easy | Portal Vein, Tardus Parvus &amp; Liver Waveforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=1kuYwCDc0tM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical Radiology by RADIOBITE</t>
   </si>
   <si>
     <t xml:space="preserve">Qidiruvdagi ma’lumot</t>
@@ -9600,7 +9678,7 @@
       </c>
       <c r="E61" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A61,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A61&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
@@ -10435,7 +10513,7 @@
       </c>
       <c r="E94" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A94,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A94&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7" t="s">
@@ -12447,7 +12525,7 @@
       </c>
       <c r="E174" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A174,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A174&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F174" s="7"/>
       <c r="G174" s="7"/>
@@ -12522,7 +12600,7 @@
       </c>
       <c r="E177" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A177,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A177&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F177" s="7"/>
       <c r="G177" s="7"/>
@@ -12547,7 +12625,7 @@
       </c>
       <c r="E178" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A178,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A178&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F178" s="7"/>
       <c r="G178" s="7"/>
@@ -12572,7 +12650,7 @@
       </c>
       <c r="E179" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A179,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A179&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F179" s="7"/>
       <c r="G179" s="7"/>
@@ -17259,7 +17337,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y298"/>
+  <dimension ref="A1:Y305"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -36145,7 +36223,7 @@
       </c>
       <c r="Y292" s="13"/>
     </row>
-    <row r="293" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="7" t="s">
         <v>2125</v>
       </c>
@@ -36210,7 +36288,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="294" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="7" t="s">
         <v>2131</v>
       </c>
@@ -36277,7 +36355,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="7" t="s">
         <v>2134</v>
       </c>
@@ -36342,7 +36420,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="7" t="s">
         <v>2137</v>
       </c>
@@ -36409,7 +36487,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="7" t="s">
         <v>2141</v>
       </c>
@@ -36476,7 +36554,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="7" t="s">
         <v>2145</v>
       </c>
@@ -36543,8 +36621,467 @@
         <v>2130</v>
       </c>
     </row>
+    <row r="299" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="7" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B299" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C299" s="7"/>
+      <c r="D299" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B299,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.2. Karotid va vertebral arteriyalar.</v>
+      </c>
+      <c r="E299" s="7" t="s">
+        <v>2151</v>
+      </c>
+      <c r="F299" s="12" t="s">
+        <v>2152</v>
+      </c>
+      <c r="G299" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="H299" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="I299" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J299" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K299" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L299" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="M299" s="7" t="s">
+        <v>897</v>
+      </c>
+      <c r="N299" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O299" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P299" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q299" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R299" s="13"/>
+      <c r="S299" s="13"/>
+      <c r="T299" s="13"/>
+      <c r="U299" s="13"/>
+      <c r="V299" s="13"/>
+      <c r="W299" s="13"/>
+      <c r="X299" s="7" t="str">
+        <f aca="false">IF(COUNT(R299:W299)=6,SUM(R299:W299),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y299" s="13" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="7" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B300" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C300" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="D300" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B300,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.2. Karotid va vertebral arteriyalar.</v>
+      </c>
+      <c r="E300" s="7" t="s">
+        <v>2155</v>
+      </c>
+      <c r="F300" s="12" t="s">
+        <v>2156</v>
+      </c>
+      <c r="G300" s="7" t="s">
+        <v>2044</v>
+      </c>
+      <c r="H300" s="7" t="s">
+        <v>2045</v>
+      </c>
+      <c r="I300" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J300" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K300" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L300" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="M300" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="N300" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O300" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P300" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q300" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R300" s="13"/>
+      <c r="S300" s="13"/>
+      <c r="T300" s="13"/>
+      <c r="U300" s="13"/>
+      <c r="V300" s="13"/>
+      <c r="W300" s="13"/>
+      <c r="X300" s="7" t="str">
+        <f aca="false">IF(COUNT(R300:W300)=6,SUM(R300:W300),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y300" s="13" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="7" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B301" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="C301" s="7"/>
+      <c r="D301" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B301,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.5. Chuqur vena trombozi: kompressiya va Doppler.</v>
+      </c>
+      <c r="E301" s="7" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F301" s="12" t="s">
+        <v>2159</v>
+      </c>
+      <c r="G301" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H301" s="7" t="s">
+        <v>1777</v>
+      </c>
+      <c r="I301" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J301" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K301" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L301" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="M301" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="N301" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O301" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P301" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q301" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R301" s="13"/>
+      <c r="S301" s="13"/>
+      <c r="T301" s="13"/>
+      <c r="U301" s="13"/>
+      <c r="V301" s="13"/>
+      <c r="W301" s="13"/>
+      <c r="X301" s="7" t="str">
+        <f aca="false">IF(COUNT(R301:W301)=6,SUM(R301:W301),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y301" s="13" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="302" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="7" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B302" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="C302" s="7"/>
+      <c r="D302" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B302,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.6. Yuzaki venalar va varikoz.</v>
+      </c>
+      <c r="E302" s="7" t="s">
+        <v>2161</v>
+      </c>
+      <c r="F302" s="12" t="s">
+        <v>2162</v>
+      </c>
+      <c r="G302" s="7" t="s">
+        <v>1344</v>
+      </c>
+      <c r="H302" s="7" t="s">
+        <v>2163</v>
+      </c>
+      <c r="I302" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J302" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K302" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L302" s="7" t="s">
+        <v>1683</v>
+      </c>
+      <c r="M302" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="N302" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O302" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P302" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q302" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R302" s="13"/>
+      <c r="S302" s="13"/>
+      <c r="T302" s="13"/>
+      <c r="U302" s="13"/>
+      <c r="V302" s="13"/>
+      <c r="W302" s="13"/>
+      <c r="X302" s="7" t="str">
+        <f aca="false">IF(COUNT(R302:W302)=6,SUM(R302:W302),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y302" s="13" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="303" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="7" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B303" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C303" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D303" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B303,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.7. Qorin aortasi va pastki kava vena.</v>
+      </c>
+      <c r="E303" s="7" t="s">
+        <v>2165</v>
+      </c>
+      <c r="F303" s="12" t="s">
+        <v>2166</v>
+      </c>
+      <c r="G303" s="7" t="s">
+        <v>2167</v>
+      </c>
+      <c r="H303" s="7" t="s">
+        <v>2168</v>
+      </c>
+      <c r="I303" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J303" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K303" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L303" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="M303" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="N303" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O303" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P303" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q303" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R303" s="13"/>
+      <c r="S303" s="13"/>
+      <c r="T303" s="13"/>
+      <c r="U303" s="13"/>
+      <c r="V303" s="13"/>
+      <c r="W303" s="13"/>
+      <c r="X303" s="7" t="str">
+        <f aca="false">IF(COUNT(R303:W303)=6,SUM(R303:W303),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y303" s="13" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="304" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A304" s="7" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B304" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C304" s="7"/>
+      <c r="D304" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B304,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>10.4. Portal gipertenziya, portal va jigar venalari.</v>
+      </c>
+      <c r="E304" s="7" t="s">
+        <v>2170</v>
+      </c>
+      <c r="F304" s="12" t="s">
+        <v>2171</v>
+      </c>
+      <c r="G304" s="7" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H304" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="I304" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J304" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K304" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L304" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="M304" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="N304" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O304" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P304" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q304" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R304" s="13"/>
+      <c r="S304" s="13"/>
+      <c r="T304" s="13"/>
+      <c r="U304" s="13"/>
+      <c r="V304" s="13"/>
+      <c r="W304" s="13"/>
+      <c r="X304" s="7" t="str">
+        <f aca="false">IF(COUNT(R304:W304)=6,SUM(R304:W304),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y304" s="13" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="305" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="7" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B305" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C305" s="7"/>
+      <c r="D305" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B305,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>10.4. Portal gipertenziya, portal va jigar venalari.</v>
+      </c>
+      <c r="E305" s="7" t="s">
+        <v>2173</v>
+      </c>
+      <c r="F305" s="12" t="s">
+        <v>2174</v>
+      </c>
+      <c r="G305" s="7" t="s">
+        <v>2175</v>
+      </c>
+      <c r="H305" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="I305" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J305" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K305" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L305" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="M305" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="N305" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O305" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P305" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q305" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R305" s="13"/>
+      <c r="S305" s="13"/>
+      <c r="T305" s="13"/>
+      <c r="U305" s="13"/>
+      <c r="V305" s="13"/>
+      <c r="W305" s="13"/>
+      <c r="X305" s="7" t="str">
+        <f aca="false">IF(COUNT(R305:W305)=6,SUM(R305:W305),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y305" s="13" t="s">
+        <v>2153</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y298"/>
+  <autoFilter ref="A1:Y305"/>
   <dataValidations count="1">
     <dataValidation allowBlank="true" error="0 dan 5 gacha butun son" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:W492" type="whole">
       <formula1>0</formula1>
@@ -36849,6 +37386,13 @@
     <hyperlink ref="F296" r:id="rId295" display="https://www.youtube.com/watch?v=fyegmq-hMhI"/>
     <hyperlink ref="F297" r:id="rId296" display="https://www.youtube.com/watch?v=HFpPPCS1wAw"/>
     <hyperlink ref="F298" r:id="rId297" display="https://www.youtube.com/watch?v=BnucQlkwEk4"/>
+    <hyperlink ref="F299" r:id="rId298" display="https://www.youtube.com/watch?v=sOwTdJPSBeI"/>
+    <hyperlink ref="F300" r:id="rId299" display="https://www.youtube.com/watch?v=fWYo00L5w6o"/>
+    <hyperlink ref="F301" r:id="rId300" display="https://www.youtube.com/watch?v=zFtlbk2yzn8"/>
+    <hyperlink ref="F302" r:id="rId301" display="https://www.youtube.com/watch?v=JwIWZuq5o14"/>
+    <hyperlink ref="F303" r:id="rId302" display="https://www.youtube.com/watch?v=QaQNYFjvKxs"/>
+    <hyperlink ref="F304" r:id="rId303" display="https://www.youtube.com/watch?v=R_BbuhzjQzc"/>
+    <hyperlink ref="F305" r:id="rId304" display="https://www.youtube.com/watch?v=1kuYwCDc0tM"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -36857,7 +37401,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId298"/>
+  <drawing r:id="rId305"/>
 </worksheet>
 </file>
 
@@ -36879,195 +37423,195 @@
         <v>746</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2150</v>
+        <v>2176</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2151</v>
+        <v>2177</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>2152</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>2153</v>
+        <v>2179</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>2154</v>
+        <v>2180</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2155</v>
+        <v>2181</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>2156</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>2157</v>
+        <v>2183</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>2158</v>
+        <v>2184</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2159</v>
+        <v>2185</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>2156</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>2160</v>
+        <v>2186</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>2161</v>
+        <v>2187</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2162</v>
+        <v>2188</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2156</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>2163</v>
+        <v>2189</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2164</v>
+        <v>2190</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2165</v>
+        <v>2191</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>2156</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>2166</v>
+        <v>2192</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>2167</v>
+        <v>2193</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2168</v>
+        <v>2194</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>2169</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>2170</v>
+        <v>2196</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>2171</v>
+        <v>2197</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2172</v>
+        <v>2198</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>2174</v>
+        <v>2200</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>2175</v>
+        <v>2201</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2176</v>
+        <v>2202</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>2177</v>
+        <v>2203</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>2178</v>
+        <v>2204</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2179</v>
+        <v>2205</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>2181</v>
+        <v>2207</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>2182</v>
+        <v>2208</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>2183</v>
+        <v>2209</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>2184</v>
+        <v>2210</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>2185</v>
+        <v>2211</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>2186</v>
+        <v>2212</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>2187</v>
+        <v>2213</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>2188</v>
+        <v>2214</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>2189</v>
+        <v>2215</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>2169</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>2190</v>
+        <v>2216</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>2191</v>
+        <v>2217</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2192</v>
+        <v>2218</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>2193</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>2194</v>
+        <v>2220</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>2195</v>
+        <v>2221</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2196</v>
+        <v>2222</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37078,10 +37622,10 @@
         <v>962</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2197</v>
+        <v>2223</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2198</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37092,10 +37636,10 @@
         <v>1054</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2197</v>
+        <v>2223</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2198</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37106,430 +37650,430 @@
         <v>1060</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2197</v>
+        <v>2223</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>2198</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>2199</v>
+        <v>2225</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>2200</v>
+        <v>2226</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2179</v>
+        <v>2205</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>2201</v>
+        <v>2227</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>2202</v>
+        <v>2228</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2183</v>
+        <v>2209</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>2203</v>
+        <v>2229</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>2204</v>
+        <v>2230</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2205</v>
+        <v>2231</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>2206</v>
+        <v>2232</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>2207</v>
+        <v>2233</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2208</v>
+        <v>2234</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>2209</v>
+        <v>2235</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>2210</v>
+        <v>2236</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2211</v>
+        <v>2237</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>2212</v>
+        <v>2238</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>2213</v>
+        <v>2239</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2211</v>
+        <v>2237</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>2214</v>
+        <v>2240</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>2215</v>
+        <v>2241</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2211</v>
+        <v>2237</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>2216</v>
+        <v>2242</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>2217</v>
+        <v>2243</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2218</v>
+        <v>2244</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>2219</v>
+        <v>2245</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>2220</v>
+        <v>2246</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>2221</v>
+        <v>2247</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>2222</v>
+        <v>2248</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>2223</v>
+        <v>2249</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>2224</v>
+        <v>2250</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>2225</v>
+        <v>2251</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>2226</v>
+        <v>2252</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>2227</v>
+        <v>2253</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>2228</v>
+        <v>2254</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>2229</v>
+        <v>2255</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>2230</v>
+        <v>2256</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>2231</v>
+        <v>2257</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>2232</v>
+        <v>2258</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>2218</v>
+        <v>2244</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>2233</v>
+        <v>2259</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>2234</v>
+        <v>2260</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>2211</v>
+        <v>2237</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>2235</v>
+        <v>2261</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>2236</v>
+        <v>2262</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>2211</v>
+        <v>2237</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>2237</v>
+        <v>2263</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>2238</v>
+        <v>2264</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>2218</v>
+        <v>2244</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>2239</v>
+        <v>2265</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>2240</v>
+        <v>2266</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>2211</v>
+        <v>2237</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>2241</v>
+        <v>2267</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>2242</v>
+        <v>2268</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>2218</v>
+        <v>2244</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>2243</v>
+        <v>2269</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>2270</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>2244</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>2218</v>
-      </c>
       <c r="D36" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>2245</v>
+        <v>2271</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>2246</v>
+        <v>2272</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>2218</v>
+        <v>2244</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>2247</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>2248</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>2221</v>
-      </c>
       <c r="D38" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>2249</v>
+        <v>2275</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>2250</v>
+        <v>2276</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>2251</v>
+        <v>2277</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>2252</v>
+        <v>2278</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>2253</v>
+        <v>2279</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>2254</v>
+        <v>2280</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>2255</v>
+        <v>2281</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>2256</v>
+        <v>2282</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>2211</v>
+        <v>2237</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>2180</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>2257</v>
+        <v>2283</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>2258</v>
+        <v>2284</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>2259</v>
+        <v>2285</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>2260</v>
+        <v>2286</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>2261</v>
+        <v>2287</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>2259</v>
+        <v>2285</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>2262</v>
+        <v>2288</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>2263</v>
+        <v>2289</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>2259</v>
+        <v>2285</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>2264</v>
+        <v>2290</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>2265</v>
+        <v>2291</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>2259</v>
+        <v>2285</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>2266</v>
+        <v>2292</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>2267</v>
+        <v>2293</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>2259</v>
+        <v>2285</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>2268</v>
+        <v>2294</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>2269</v>
+        <v>2295</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>2259</v>
+        <v>2285</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>2173</v>
+        <v>2199</v>
       </c>
     </row>
   </sheetData>
@@ -37615,22 +38159,22 @@
         <v>36</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2270</v>
+        <v>2296</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>2271</v>
+        <v>2297</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>2272</v>
+        <v>2298</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>2273</v>
+        <v>2299</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>2274</v>
+        <v>2300</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>2193</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38692,7 +39236,7 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="17"/>
       <c r="B35" s="17" t="s">
-        <v>2275</v>
+        <v>2301</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">SUM(C2:C34)</f>
@@ -38721,26 +39265,26 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>2276</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>2277</v>
+        <v>2303</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>2278</v>
+        <v>2304</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>2279</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>2280</v>
+        <v>2306</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>2281</v>
+        <v>2307</v>
       </c>
       <c r="C39" s="16" t="n">
         <f aca="false">C35/253</f>
@@ -38749,10 +39293,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>2282</v>
+        <v>2308</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>2283</v>
+        <v>2309</v>
       </c>
       <c r="C40" s="16" t="n">
         <f aca="false">E35</f>
@@ -38761,10 +39305,10 @@
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>2284</v>
+        <v>2310</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>2285</v>
+        <v>2311</v>
       </c>
       <c r="C41" s="16" t="n">
         <f aca="false">SUM(D2:D7)/SUM(C2:C7)</f>
@@ -38773,10 +39317,10 @@
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>2286</v>
+        <v>2312</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>2287</v>
+        <v>2313</v>
       </c>
       <c r="C42" s="16" t="n">
         <f aca="false">(COUNTIF(Katalog!$Q$2:$Q$298,"Havola tekshirilgan*")+COUNTIF(Katalog!$Q$2:$Q$298,"Metadata tekshirilgan*"))/COUNTA(Katalog!$A$2:$A$298)</f>
@@ -38785,10 +39329,10 @@
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>2288</v>
+        <v>2314</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>2289</v>
+        <v>2315</v>
       </c>
       <c r="C43" s="16" t="n">
         <f aca="false">COUNT(Katalog!$X$2:$X$298)/COUNTA(Katalog!$A$2:$A$298)</f>
@@ -38823,400 +39367,400 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2290</v>
+        <v>2316</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2291</v>
+        <v>2317</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2292</v>
+        <v>2318</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>2293</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>2294</v>
+        <v>2320</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>2295</v>
+        <v>2321</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2296</v>
+        <v>2322</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>2297</v>
+        <v>2323</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>2298</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>2299</v>
+        <v>2325</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>2300</v>
+        <v>2326</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2301</v>
+        <v>2327</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>2302</v>
+        <v>2328</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>2303</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>2304</v>
+        <v>2330</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>2305</v>
+        <v>2331</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2306</v>
+        <v>2332</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2307</v>
+        <v>2333</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>2308</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>2309</v>
+        <v>2335</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2310</v>
+        <v>2336</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2311</v>
+        <v>2337</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>2307</v>
+        <v>2333</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>2312</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>2313</v>
+        <v>2339</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>2314</v>
+        <v>2340</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2315</v>
+        <v>2341</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>2307</v>
+        <v>2333</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>2316</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>2317</v>
+        <v>2343</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>2318</v>
+        <v>2344</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2319</v>
+        <v>2345</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>2307</v>
+        <v>2333</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>2320</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>2321</v>
+        <v>2347</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>2322</v>
+        <v>2348</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2323</v>
+        <v>2349</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>2324</v>
+        <v>2350</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>2325</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>2326</v>
+        <v>2352</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>2327</v>
+        <v>2353</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2328</v>
+        <v>2354</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>2329</v>
+        <v>2355</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>2330</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>2331</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>2332</v>
+        <v>2358</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>2333</v>
+        <v>2359</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>2151</v>
+        <v>2177</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>2334</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>2335</v>
+        <v>2361</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>2336</v>
+        <v>2362</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2337</v>
+        <v>2363</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>2338</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>2335</v>
+        <v>2361</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>2339</v>
+        <v>2365</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2340</v>
+        <v>2366</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2341</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>2335</v>
+        <v>2361</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>2342</v>
+        <v>2368</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2343</v>
+        <v>2369</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2344</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>2335</v>
+        <v>2361</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>2345</v>
+        <v>2371</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2346</v>
+        <v>2372</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2347</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>2335</v>
+        <v>2361</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>2348</v>
+        <v>2374</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2349</v>
+        <v>2375</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>2350</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>2335</v>
+        <v>2361</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>2351</v>
+        <v>2377</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2352</v>
+        <v>2378</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2353</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>2354</v>
+        <v>2380</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>95</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2355</v>
+        <v>2381</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2356</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>2357</v>
+        <v>2383</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2358</v>
+        <v>2384</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>2359</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>2357</v>
+        <v>2383</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2360</v>
+        <v>2386</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>2361</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>2357</v>
+        <v>2383</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>2362</v>
+        <v>2388</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2363</v>
+        <v>2389</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>2364</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>2357</v>
+        <v>2383</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>2365</v>
+        <v>2391</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2366</v>
+        <v>2392</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>2367</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>2273</v>
+        <v>2299</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2368</v>
+        <v>2394</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2369</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>2273</v>
+        <v>2299</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>201</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2370</v>
+        <v>2396</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>2371</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>2273</v>
+        <v>2299</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>354</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>2372</v>
+        <v>2398</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>2373</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>2374</v>
+        <v>2400</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>482</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>2375</v>
+        <v>2401</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>2376</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>2377</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>2378</v>
+        <v>2404</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>2379</v>
+        <v>2405</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>2380</v>
+        <v>2406</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>41</v>
@@ -39224,86 +39768,86 @@
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>2381</v>
+        <v>2407</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>2382</v>
+        <v>2408</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>2383</v>
+        <v>2409</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>2384</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>2385</v>
+        <v>2411</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>2386</v>
+        <v>2412</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>2387</v>
+        <v>2413</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>2384</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>2388</v>
+        <v>2414</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>2389</v>
+        <v>2415</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>2390</v>
+        <v>2416</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>2391</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>2392</v>
+        <v>2418</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>2393</v>
+        <v>2419</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>2394</v>
+        <v>2420</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>2395</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>2396</v>
+        <v>2422</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>2397</v>
+        <v>2423</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>2398</v>
+        <v>2424</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>2399</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>2400</v>
+        <v>2426</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>2401</v>
+        <v>2427</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>2402</v>
+        <v>2428</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>2403</v>
+        <v>2429</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
+++ b/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Audit" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Katalog!$A$1:$Y$305</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Katalog!$A$1:$Y$308</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Mundarija!$A$1:$I$254</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Qidiruv navbati'!$A$1:$F$117</definedName>
   </definedNames>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7023" uniqueCount="2430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7070" uniqueCount="2441">
   <si>
     <t xml:space="preserve">SHOKALON — videodarslar katalogi, 7-versiya</t>
   </si>
@@ -6560,6 +6560,39 @@
   </si>
   <si>
     <t xml:space="preserve">Medical Radiology by RADIOBITE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carotid and Vertebral Arteries Doppler Ultrasound Protocols</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=r8egrNqH2YU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03.15.01; 03.15.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplex Exam of Aorta and IVC - Case Study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=tqt1Wr5-q-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MintMedical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVC Ultrasound | How to assess the IVC for volume status using ultrasound | Clarius Ultrasound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=j5aboEF2-qo</t>
   </si>
   <si>
     <t xml:space="preserve">Qidiruvdagi ma’lumot</t>
@@ -10486,7 +10519,7 @@
       </c>
       <c r="E93" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A93,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A93&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7" t="s">
@@ -10513,7 +10546,7 @@
       </c>
       <c r="E94" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A94,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A94&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7" t="s">
@@ -12525,7 +12558,7 @@
       </c>
       <c r="E174" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A174,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A174&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F174" s="7"/>
       <c r="G174" s="7"/>
@@ -12650,7 +12683,7 @@
       </c>
       <c r="E179" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A179,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A179&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F179" s="7"/>
       <c r="G179" s="7"/>
@@ -13679,13 +13712,13 @@
       </c>
       <c r="E220" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A220,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A220&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220" s="7"/>
       <c r="G220" s="7"/>
       <c r="H220" s="7" t="str">
         <f aca="false">IF(G220&lt;&gt;"","Takroriy",IF(E220=0,"Yetishmaydi",IF(F220="ha","Qisman to‘ldirilgan","Mavjud, lekin tekshirilmagan")))</f>
-        <v>Yetishmaydi</v>
+        <v>Mavjud, lekin tekshirilmagan</v>
       </c>
       <c r="I220" s="7"/>
     </row>
@@ -17337,7 +17370,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y305"/>
+  <dimension ref="A1:Y308"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -36621,7 +36654,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="7" t="s">
         <v>2150</v>
       </c>
@@ -36686,7 +36719,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="7" t="s">
         <v>2154</v>
       </c>
@@ -36753,7 +36786,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="301" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="7" t="s">
         <v>2157</v>
       </c>
@@ -36818,7 +36851,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="7" t="s">
         <v>2160</v>
       </c>
@@ -36883,7 +36916,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="7" t="s">
         <v>2164</v>
       </c>
@@ -36950,7 +36983,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="7" t="s">
         <v>2169</v>
       </c>
@@ -37015,7 +37048,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="7" t="s">
         <v>2172</v>
       </c>
@@ -37080,8 +37113,201 @@
         <v>2153</v>
       </c>
     </row>
+    <row r="306" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A306" s="7" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B306" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C306" s="7"/>
+      <c r="D306" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B306,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.2. Karotid va vertebral arteriyalar.</v>
+      </c>
+      <c r="E306" s="7" t="s">
+        <v>2177</v>
+      </c>
+      <c r="F306" s="12" t="s">
+        <v>2178</v>
+      </c>
+      <c r="G306" s="7" t="s">
+        <v>1475</v>
+      </c>
+      <c r="H306" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="I306" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J306" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K306" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L306" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="M306" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="N306" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O306" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P306" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q306" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R306" s="13"/>
+      <c r="S306" s="13"/>
+      <c r="T306" s="13"/>
+      <c r="U306" s="13"/>
+      <c r="V306" s="13"/>
+      <c r="W306" s="13"/>
+      <c r="X306" s="7" t="str">
+        <f aca="false">IF(COUNT(R306:W306)=6,SUM(R306:W306),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y306" s="13"/>
+    </row>
+    <row r="307" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A307" s="7" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B307" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C307" s="7" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D307" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B307,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.7. Qorin aortasi va pastki kava vena.</v>
+      </c>
+      <c r="E307" s="7" t="s">
+        <v>2181</v>
+      </c>
+      <c r="F307" s="12" t="s">
+        <v>2182</v>
+      </c>
+      <c r="G307" s="7" t="s">
+        <v>2183</v>
+      </c>
+      <c r="H307" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="I307" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J307" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K307" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L307" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="M307" s="7" t="s">
+        <v>1648</v>
+      </c>
+      <c r="N307" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O307" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P307" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q307" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R307" s="13"/>
+      <c r="S307" s="13"/>
+      <c r="T307" s="13"/>
+      <c r="U307" s="13"/>
+      <c r="V307" s="13"/>
+      <c r="W307" s="13"/>
+      <c r="X307" s="7" t="str">
+        <f aca="false">IF(COUNT(R307:W307)=6,SUM(R307:W307),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y307" s="13"/>
+    </row>
+    <row r="308" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A308" s="7" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B308" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C308" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="D308" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B308,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>15.2. Pastki kava vena va uning klinik ahamiyati.</v>
+      </c>
+      <c r="E308" s="7" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F308" s="12" t="s">
+        <v>2186</v>
+      </c>
+      <c r="G308" s="7" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H308" s="7" t="s">
+        <v>1575</v>
+      </c>
+      <c r="I308" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J308" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K308" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L308" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="M308" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="N308" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O308" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P308" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q308" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R308" s="13"/>
+      <c r="S308" s="13"/>
+      <c r="T308" s="13"/>
+      <c r="U308" s="13"/>
+      <c r="V308" s="13"/>
+      <c r="W308" s="13"/>
+      <c r="X308" s="7" t="str">
+        <f aca="false">IF(COUNT(R308:W308)=6,SUM(R308:W308),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y308" s="13"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y305"/>
+  <autoFilter ref="A1:Y308"/>
   <dataValidations count="1">
     <dataValidation allowBlank="true" error="0 dan 5 gacha butun son" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:W492" type="whole">
       <formula1>0</formula1>
@@ -37393,6 +37619,9 @@
     <hyperlink ref="F303" r:id="rId302" display="https://www.youtube.com/watch?v=QaQNYFjvKxs"/>
     <hyperlink ref="F304" r:id="rId303" display="https://www.youtube.com/watch?v=R_BbuhzjQzc"/>
     <hyperlink ref="F305" r:id="rId304" display="https://www.youtube.com/watch?v=1kuYwCDc0tM"/>
+    <hyperlink ref="F306" r:id="rId305" display="https://www.youtube.com/watch?v=r8egrNqH2YU"/>
+    <hyperlink ref="F307" r:id="rId306" display="https://www.youtube.com/watch?v=tqt1Wr5-q-E"/>
+    <hyperlink ref="F308" r:id="rId307" display="https://www.youtube.com/watch?v=j5aboEF2-qo"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -37401,7 +37630,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId305"/>
+  <drawing r:id="rId308"/>
 </worksheet>
 </file>
 
@@ -37423,195 +37652,195 @@
         <v>746</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2176</v>
+        <v>2187</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2177</v>
+        <v>2188</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>2178</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>2179</v>
+        <v>2190</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>2180</v>
+        <v>2191</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2181</v>
+        <v>2192</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>2182</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>2183</v>
+        <v>2194</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>2184</v>
+        <v>2195</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2185</v>
+        <v>2196</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>2182</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>2186</v>
+        <v>2197</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>2187</v>
+        <v>2198</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2188</v>
+        <v>2199</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2182</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>2189</v>
+        <v>2200</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2190</v>
+        <v>2201</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2191</v>
+        <v>2202</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>2182</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>2192</v>
+        <v>2203</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>2193</v>
+        <v>2204</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2194</v>
+        <v>2205</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>2195</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>2196</v>
+        <v>2207</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>2197</v>
+        <v>2208</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2198</v>
+        <v>2209</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>2200</v>
+        <v>2211</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>2201</v>
+        <v>2212</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2202</v>
+        <v>2213</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>2203</v>
+        <v>2214</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>2204</v>
+        <v>2215</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2205</v>
+        <v>2216</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>2207</v>
+        <v>2218</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>2208</v>
+        <v>2219</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>2209</v>
+        <v>2220</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>2210</v>
+        <v>2221</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>2211</v>
+        <v>2222</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>2212</v>
+        <v>2223</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>2213</v>
+        <v>2224</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>2214</v>
+        <v>2225</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>2215</v>
+        <v>2226</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>2195</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>2216</v>
+        <v>2227</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>2217</v>
+        <v>2228</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2218</v>
+        <v>2229</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>2219</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>2220</v>
+        <v>2231</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>2221</v>
+        <v>2232</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2222</v>
+        <v>2233</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37622,10 +37851,10 @@
         <v>962</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2224</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37636,10 +37865,10 @@
         <v>1054</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2224</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37650,430 +37879,430 @@
         <v>1060</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>2224</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>2225</v>
+        <v>2236</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>2226</v>
+        <v>2237</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2205</v>
+        <v>2216</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>2227</v>
+        <v>2238</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>2228</v>
+        <v>2239</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2209</v>
+        <v>2220</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>2229</v>
+        <v>2240</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2231</v>
+        <v>2242</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>2232</v>
+        <v>2243</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>2233</v>
+        <v>2244</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2234</v>
+        <v>2245</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>2235</v>
+        <v>2246</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>2236</v>
+        <v>2247</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2237</v>
+        <v>2248</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>2238</v>
+        <v>2249</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>2239</v>
+        <v>2250</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2237</v>
+        <v>2248</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>2240</v>
+        <v>2251</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>2241</v>
+        <v>2252</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2237</v>
+        <v>2248</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>2242</v>
+        <v>2253</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>2243</v>
+        <v>2254</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2244</v>
+        <v>2255</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>2245</v>
+        <v>2256</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>2246</v>
+        <v>2257</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>2247</v>
+        <v>2258</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>2248</v>
+        <v>2259</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>2249</v>
+        <v>2260</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>2250</v>
+        <v>2261</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>2251</v>
+        <v>2262</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>2252</v>
+        <v>2263</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>2253</v>
+        <v>2264</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>2254</v>
+        <v>2265</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>2255</v>
+        <v>2266</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>2256</v>
+        <v>2267</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>2257</v>
+        <v>2268</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>2258</v>
+        <v>2269</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>2244</v>
+        <v>2255</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>2259</v>
+        <v>2270</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>2260</v>
+        <v>2271</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>2237</v>
+        <v>2248</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>2261</v>
+        <v>2272</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>2262</v>
+        <v>2273</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>2237</v>
+        <v>2248</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>2263</v>
+        <v>2274</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>2264</v>
+        <v>2275</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>2244</v>
+        <v>2255</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>2265</v>
+        <v>2276</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>2266</v>
+        <v>2277</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>2237</v>
+        <v>2248</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>2267</v>
+        <v>2278</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>2268</v>
+        <v>2279</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>2244</v>
+        <v>2255</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>2269</v>
+        <v>2280</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>2270</v>
+        <v>2281</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>2244</v>
+        <v>2255</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>2271</v>
+        <v>2282</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>2272</v>
+        <v>2283</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>2244</v>
+        <v>2255</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>2273</v>
+        <v>2284</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>2274</v>
+        <v>2285</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>2247</v>
+        <v>2258</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>2275</v>
+        <v>2286</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>2276</v>
+        <v>2287</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>2277</v>
+        <v>2288</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>2278</v>
+        <v>2289</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>2279</v>
+        <v>2290</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>2280</v>
+        <v>2291</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>2281</v>
+        <v>2292</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>2282</v>
+        <v>2293</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>2237</v>
+        <v>2248</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>2283</v>
+        <v>2294</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>2284</v>
+        <v>2295</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>2285</v>
+        <v>2296</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>2286</v>
+        <v>2297</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>2287</v>
+        <v>2298</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>2285</v>
+        <v>2296</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>2288</v>
+        <v>2299</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>2289</v>
+        <v>2300</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>2285</v>
+        <v>2296</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>2290</v>
+        <v>2301</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>2291</v>
+        <v>2302</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>2285</v>
+        <v>2296</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>2292</v>
+        <v>2303</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>2293</v>
+        <v>2304</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>2285</v>
+        <v>2296</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>2294</v>
+        <v>2305</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>2295</v>
+        <v>2306</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>2285</v>
+        <v>2296</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>2199</v>
+        <v>2210</v>
       </c>
     </row>
   </sheetData>
@@ -38159,22 +38388,22 @@
         <v>36</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2296</v>
+        <v>2307</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>2297</v>
+        <v>2308</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>2298</v>
+        <v>2309</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>2299</v>
+        <v>2310</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>2300</v>
+        <v>2311</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>2219</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39086,15 +39315,15 @@
       </c>
       <c r="D30" s="7" t="n">
         <f aca="false">COUNTIFS(Mundarija!$C$2:$C$254,B30,Mundarija!$E$2:$E$254,"&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="16" t="n">
         <f aca="false">IF(C30=0,0,D30/C30)</f>
-        <v>0</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="F30" s="7" t="n">
         <f aca="false">COUNTIFS(Mundarija!$C$2:$C$254,B30,Mundarija!$H$2:$H$254,"Yetishmaydi")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G30" s="7" t="n">
         <f aca="false">COUNTIFS(Mundarija!$C$2:$C$254,B30,Mundarija!$H$2:$H$254,"Qisman to‘ldirilgan")</f>
@@ -39236,7 +39465,7 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="17"/>
       <c r="B35" s="17" t="s">
-        <v>2301</v>
+        <v>2312</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">SUM(C2:C34)</f>
@@ -39244,15 +39473,15 @@
       </c>
       <c r="D35" s="17" t="n">
         <f aca="false">SUM(D2:D34)</f>
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E35" s="18" t="n">
         <f aca="false">IF(C35=0,0,D35/C35)</f>
-        <v>0.703557312252965</v>
+        <v>0.707509881422925</v>
       </c>
       <c r="F35" s="17" t="n">
         <f aca="false">SUM(F2:F34)</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G35" s="17" t="n">
         <f aca="false">SUM(G2:G34)</f>
@@ -39265,26 +39494,26 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>2302</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>2303</v>
+        <v>2314</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>2304</v>
+        <v>2315</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>2305</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>2306</v>
+        <v>2317</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>2307</v>
+        <v>2318</v>
       </c>
       <c r="C39" s="16" t="n">
         <f aca="false">C35/253</f>
@@ -39293,22 +39522,22 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>2308</v>
+        <v>2319</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>2309</v>
+        <v>2320</v>
       </c>
       <c r="C40" s="16" t="n">
         <f aca="false">E35</f>
-        <v>0.703557312252965</v>
+        <v>0.707509881422925</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>2310</v>
+        <v>2321</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>2311</v>
+        <v>2322</v>
       </c>
       <c r="C41" s="16" t="n">
         <f aca="false">SUM(D2:D7)/SUM(C2:C7)</f>
@@ -39317,10 +39546,10 @@
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>2312</v>
+        <v>2323</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>2313</v>
+        <v>2324</v>
       </c>
       <c r="C42" s="16" t="n">
         <f aca="false">(COUNTIF(Katalog!$Q$2:$Q$298,"Havola tekshirilgan*")+COUNTIF(Katalog!$Q$2:$Q$298,"Metadata tekshirilgan*"))/COUNTA(Katalog!$A$2:$A$298)</f>
@@ -39329,10 +39558,10 @@
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>2314</v>
+        <v>2325</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>2315</v>
+        <v>2326</v>
       </c>
       <c r="C43" s="16" t="n">
         <f aca="false">COUNT(Katalog!$X$2:$X$298)/COUNTA(Katalog!$A$2:$A$298)</f>
@@ -39367,400 +39596,400 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2316</v>
+        <v>2327</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2317</v>
+        <v>2328</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2318</v>
+        <v>2329</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>2319</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>2320</v>
+        <v>2331</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>2321</v>
+        <v>2332</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2322</v>
+        <v>2333</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>2323</v>
+        <v>2334</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>2324</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>2325</v>
+        <v>2336</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>2326</v>
+        <v>2337</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2327</v>
+        <v>2338</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>2328</v>
+        <v>2339</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>2329</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>2330</v>
+        <v>2341</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>2331</v>
+        <v>2342</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2332</v>
+        <v>2343</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2333</v>
+        <v>2344</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>2334</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>2335</v>
+        <v>2346</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2336</v>
+        <v>2347</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2337</v>
+        <v>2348</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>2333</v>
+        <v>2344</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>2338</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>2339</v>
+        <v>2350</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>2340</v>
+        <v>2351</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2341</v>
+        <v>2352</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>2333</v>
+        <v>2344</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>2342</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>2343</v>
+        <v>2354</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>2355</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>2356</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>2344</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>2345</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>2333</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>2346</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>2347</v>
+        <v>2358</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>2348</v>
+        <v>2359</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2349</v>
+        <v>2360</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>2350</v>
+        <v>2361</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>2351</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>2352</v>
+        <v>2363</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>2353</v>
+        <v>2364</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2354</v>
+        <v>2365</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>2355</v>
+        <v>2366</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>2356</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>2357</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>2358</v>
+        <v>2369</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>2359</v>
+        <v>2370</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>2177</v>
+        <v>2188</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>2360</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>2361</v>
+        <v>2372</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>2362</v>
+        <v>2373</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2363</v>
+        <v>2374</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>2364</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>2361</v>
+        <v>2372</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>2365</v>
+        <v>2376</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2366</v>
+        <v>2377</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2367</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>2361</v>
+        <v>2372</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>2368</v>
+        <v>2379</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2369</v>
+        <v>2380</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2370</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>2361</v>
+        <v>2372</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>2371</v>
+        <v>2382</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2372</v>
+        <v>2383</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2373</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>2361</v>
+        <v>2372</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>2374</v>
+        <v>2385</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2375</v>
+        <v>2386</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>2376</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>2361</v>
+        <v>2372</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>2377</v>
+        <v>2388</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2378</v>
+        <v>2389</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2379</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>2380</v>
+        <v>2391</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>95</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2381</v>
+        <v>2392</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2382</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>2383</v>
+        <v>2394</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2384</v>
+        <v>2395</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>2385</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>2383</v>
+        <v>2394</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2386</v>
+        <v>2397</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>2387</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>2383</v>
+        <v>2394</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>2388</v>
+        <v>2399</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2389</v>
+        <v>2400</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>2390</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>2383</v>
+        <v>2394</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>2391</v>
+        <v>2402</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2392</v>
+        <v>2403</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>2393</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>2299</v>
+        <v>2310</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2394</v>
+        <v>2405</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2395</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>2299</v>
+        <v>2310</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>201</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2396</v>
+        <v>2407</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>2397</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>2299</v>
+        <v>2310</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>354</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>2398</v>
+        <v>2409</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>2399</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>2400</v>
+        <v>2411</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>482</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>2401</v>
+        <v>2412</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>2402</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>2403</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>2404</v>
+        <v>2415</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>2405</v>
+        <v>2416</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>2406</v>
+        <v>2417</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>41</v>
@@ -39768,86 +39997,86 @@
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>2407</v>
+        <v>2418</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>2408</v>
+        <v>2419</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>2409</v>
+        <v>2420</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>2410</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>2411</v>
+        <v>2422</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>2412</v>
+        <v>2423</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>2413</v>
+        <v>2424</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>2410</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>2414</v>
+        <v>2425</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>2415</v>
+        <v>2426</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>2416</v>
+        <v>2427</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>2417</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>2418</v>
+        <v>2429</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>2419</v>
+        <v>2430</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>2420</v>
+        <v>2431</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>2421</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>2422</v>
+        <v>2433</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>2423</v>
+        <v>2434</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>2424</v>
+        <v>2435</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>2425</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>2426</v>
+        <v>2437</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>2427</v>
+        <v>2438</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>2428</v>
+        <v>2439</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>2429</v>
+        <v>2440</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
+++ b/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
@@ -39552,8 +39552,8 @@
         <v>2324</v>
       </c>
       <c r="C42" s="16" t="n">
-        <f aca="false">(COUNTIF(Katalog!$Q$2:$Q$298,"Havola tekshirilgan*")+COUNTIF(Katalog!$Q$2:$Q$298,"Metadata tekshirilgan*"))/COUNTA(Katalog!$A$2:$A$298)</f>
-        <v>0.98989898989899</v>
+        <f aca="false">(COUNTIF(Katalog!$Q$2:$Q$308,"Havola tekshirilgan*")+COUNTIF(Katalog!$Q$2:$Q$308,"Metadata tekshirilgan*"))/COUNTA(Katalog!$A$2:$A$308)</f>
+        <v>0.990228013029316</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39564,7 +39564,7 @@
         <v>2326</v>
       </c>
       <c r="C43" s="16" t="n">
-        <f aca="false">COUNT(Katalog!$X$2:$X$298)/COUNTA(Katalog!$A$2:$A$298)</f>
+        <f aca="false">COUNT(Katalog!$X$2:$X$308)/COUNTA(Katalog!$A$2:$A$308)</f>
         <v>0</v>
       </c>
     </row>

--- a/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
+++ b/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Audit" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Katalog!$A$1:$Y$308</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Katalog!$A$1:$Y$312</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Mundarija!$A$1:$I$254</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Qidiruv navbati'!$A$1:$F$117</definedName>
   </definedNames>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7100" uniqueCount="2446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7133" uniqueCount="2453">
   <si>
     <t xml:space="preserve">SHOKALON — videodarslar katalogi, 7-versiya</t>
   </si>
@@ -6611,6 +6611,27 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.youtube.com/watch?v=9pqoVZEEyrg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifying carotid artery disease with ultrasound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=66KjiicFGL4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faqat bitta parallel ishda topilgan; 2026-10-17 da qo‘shildi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aorta Duplex (Doppler) Protocol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=0fwT622SLB8</t>
   </si>
   <si>
     <t xml:space="preserve">Qidiruvdagi ma’lumot</t>
@@ -10534,7 +10555,7 @@
       </c>
       <c r="E93" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A93,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A93&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7" t="s">
@@ -12598,7 +12619,7 @@
       </c>
       <c r="E175" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A175,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A175&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F175" s="7"/>
       <c r="G175" s="7"/>
@@ -12698,7 +12719,7 @@
       </c>
       <c r="E179" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A179,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A179&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F179" s="7"/>
       <c r="G179" s="7"/>
@@ -17385,7 +17406,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y310"/>
+  <dimension ref="A1:Y312"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -37447,8 +37468,140 @@
       </c>
       <c r="Y310" s="13"/>
     </row>
+    <row r="311" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="7" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B311" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C311" s="7"/>
+      <c r="D311" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B311,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.3. Aterosklerotik blyashkalar, stenoz va okklyuziya.</v>
+      </c>
+      <c r="E311" s="7" t="s">
+        <v>2194</v>
+      </c>
+      <c r="F311" s="12" t="s">
+        <v>2195</v>
+      </c>
+      <c r="G311" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H311" s="7" t="s">
+        <v>1777</v>
+      </c>
+      <c r="I311" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J311" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K311" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L311" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="M311" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="N311" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O311" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P311" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q311" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R311" s="13"/>
+      <c r="S311" s="13"/>
+      <c r="T311" s="13"/>
+      <c r="U311" s="13"/>
+      <c r="V311" s="13"/>
+      <c r="W311" s="13"/>
+      <c r="X311" s="7" t="str">
+        <f aca="false">IF(COUNT(R311:W311)=6,SUM(R311:W311),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y311" s="13" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="7" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B312" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C312" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D312" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B312,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.7. Qorin aortasi va pastki kava vena.</v>
+      </c>
+      <c r="E312" s="7" t="s">
+        <v>2198</v>
+      </c>
+      <c r="F312" s="12" t="s">
+        <v>2199</v>
+      </c>
+      <c r="G312" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="H312" s="7" t="s">
+        <v>2037</v>
+      </c>
+      <c r="I312" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J312" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K312" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L312" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="M312" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="N312" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O312" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P312" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q312" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R312" s="13"/>
+      <c r="S312" s="13"/>
+      <c r="T312" s="13"/>
+      <c r="U312" s="13"/>
+      <c r="V312" s="13"/>
+      <c r="W312" s="13"/>
+      <c r="X312" s="7" t="str">
+        <f aca="false">IF(COUNT(R312:W312)=6,SUM(R312:W312),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y312" s="13" t="s">
+        <v>2196</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y308"/>
+  <autoFilter ref="A1:Y312"/>
   <dataValidations count="1">
     <dataValidation allowBlank="true" error="0 dan 5 gacha butun son" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:W492" type="whole">
       <formula1>0</formula1>
@@ -37765,6 +37918,8 @@
     <hyperlink ref="F308" r:id="rId307" display="https://www.youtube.com/watch?v=j5aboEF2-qo"/>
     <hyperlink ref="F309" r:id="rId308" display="https://www.youtube.com/watch?v=hbVxhOV6NFw"/>
     <hyperlink ref="F310" r:id="rId309" display="https://www.youtube.com/watch?v=9pqoVZEEyrg"/>
+    <hyperlink ref="F311" r:id="rId310" display="https://www.youtube.com/watch?v=66KjiicFGL4"/>
+    <hyperlink ref="F312" r:id="rId311" display="https://www.youtube.com/watch?v=0fwT622SLB8"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -37773,7 +37928,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId310"/>
+  <drawing r:id="rId312"/>
 </worksheet>
 </file>
 
@@ -37795,195 +37950,195 @@
         <v>746</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2193</v>
+        <v>2200</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2194</v>
+        <v>2201</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>2195</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>2196</v>
+        <v>2203</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>2197</v>
+        <v>2204</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2198</v>
+        <v>2205</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>2199</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>2200</v>
+        <v>2207</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>2201</v>
+        <v>2208</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2202</v>
+        <v>2209</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>2199</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>2203</v>
+        <v>2210</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>2204</v>
+        <v>2211</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2205</v>
+        <v>2212</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2199</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>2206</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>2207</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>2208</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>2199</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>2209</v>
+        <v>2216</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>2210</v>
+        <v>2217</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2211</v>
+        <v>2218</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>2212</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>2213</v>
+        <v>2220</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>2214</v>
+        <v>2221</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2215</v>
+        <v>2222</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>2217</v>
+        <v>2224</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>2218</v>
+        <v>2225</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2219</v>
+        <v>2226</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>2220</v>
+        <v>2227</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>2221</v>
+        <v>2228</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2222</v>
+        <v>2229</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>2224</v>
+        <v>2231</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>2225</v>
+        <v>2232</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>2226</v>
+        <v>2233</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>2227</v>
+        <v>2234</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>2228</v>
+        <v>2235</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>2229</v>
+        <v>2236</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>2230</v>
+        <v>2237</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>2231</v>
+        <v>2238</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>2232</v>
+        <v>2239</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>2212</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>2233</v>
+        <v>2240</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>2234</v>
+        <v>2241</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2235</v>
+        <v>2242</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>2236</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>2237</v>
+        <v>2244</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>2238</v>
+        <v>2245</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2239</v>
+        <v>2246</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37994,10 +38149,10 @@
         <v>962</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2240</v>
+        <v>2247</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2241</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38008,10 +38163,10 @@
         <v>1054</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2240</v>
+        <v>2247</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2241</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38022,430 +38177,430 @@
         <v>1060</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2240</v>
+        <v>2247</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>2241</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>2242</v>
+        <v>2249</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>2243</v>
+        <v>2250</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2222</v>
+        <v>2229</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>2244</v>
+        <v>2251</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>2245</v>
+        <v>2252</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2226</v>
+        <v>2233</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>2246</v>
+        <v>2253</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>2247</v>
+        <v>2254</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2248</v>
+        <v>2255</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>2249</v>
+        <v>2256</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>2250</v>
+        <v>2257</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2251</v>
+        <v>2258</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>2252</v>
+        <v>2259</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>2253</v>
+        <v>2260</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2254</v>
+        <v>2261</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>2255</v>
+        <v>2262</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>2256</v>
+        <v>2263</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2254</v>
+        <v>2261</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>2257</v>
+        <v>2264</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>2258</v>
+        <v>2265</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2254</v>
+        <v>2261</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>2259</v>
+        <v>2266</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>2260</v>
+        <v>2267</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2261</v>
+        <v>2268</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>2262</v>
+        <v>2269</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>2263</v>
+        <v>2270</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>2264</v>
+        <v>2271</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>2265</v>
+        <v>2272</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>2266</v>
+        <v>2273</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>2267</v>
+        <v>2274</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>2268</v>
+        <v>2275</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>2269</v>
+        <v>2276</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>2270</v>
+        <v>2277</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>2271</v>
+        <v>2278</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>2272</v>
+        <v>2279</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>2273</v>
+        <v>2280</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>2274</v>
+        <v>2281</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>2275</v>
+        <v>2282</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>2261</v>
+        <v>2268</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>2276</v>
+        <v>2283</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>2277</v>
+        <v>2284</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>2254</v>
+        <v>2261</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>2278</v>
+        <v>2285</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>2279</v>
+        <v>2286</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>2254</v>
+        <v>2261</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>2280</v>
+        <v>2287</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>2281</v>
+        <v>2288</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>2261</v>
+        <v>2268</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>2282</v>
+        <v>2289</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>2283</v>
+        <v>2290</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>2254</v>
+        <v>2261</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>2284</v>
+        <v>2291</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>2285</v>
+        <v>2292</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>2261</v>
+        <v>2268</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>2286</v>
+        <v>2293</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>2287</v>
+        <v>2294</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>2261</v>
+        <v>2268</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>2288</v>
+        <v>2295</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>2289</v>
+        <v>2296</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>2261</v>
+        <v>2268</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>2290</v>
+        <v>2297</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>2291</v>
+        <v>2298</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>2264</v>
+        <v>2271</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>2292</v>
+        <v>2299</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>2293</v>
+        <v>2300</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>2294</v>
+        <v>2301</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>2295</v>
+        <v>2302</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>2296</v>
+        <v>2303</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>2297</v>
+        <v>2304</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>2298</v>
+        <v>2305</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>2299</v>
+        <v>2306</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>2254</v>
+        <v>2261</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>2223</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>2300</v>
+        <v>2307</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>2188</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>2301</v>
+        <v>2308</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>2302</v>
+        <v>2309</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>2303</v>
+        <v>2310</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>2301</v>
+        <v>2308</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>2304</v>
+        <v>2311</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>2305</v>
+        <v>2312</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>2301</v>
+        <v>2308</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>2306</v>
+        <v>2313</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>2307</v>
+        <v>2314</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>2301</v>
+        <v>2308</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>2308</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>2309</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>2301</v>
-      </c>
       <c r="D46" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>2310</v>
+        <v>2317</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>2311</v>
+        <v>2318</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>2301</v>
+        <v>2308</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>2216</v>
+        <v>2223</v>
       </c>
     </row>
   </sheetData>
@@ -38531,22 +38686,22 @@
         <v>36</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2312</v>
+        <v>2319</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>2313</v>
+        <v>2320</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>2314</v>
+        <v>2321</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>2315</v>
+        <v>2322</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>2316</v>
+        <v>2323</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>2236</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39608,7 +39763,7 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="17"/>
       <c r="B35" s="17" t="s">
-        <v>2317</v>
+        <v>2324</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">SUM(C2:C34)</f>
@@ -39637,26 +39792,26 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>2318</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>2319</v>
+        <v>2326</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>2320</v>
+        <v>2327</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>2321</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>2322</v>
+        <v>2329</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>2323</v>
+        <v>2330</v>
       </c>
       <c r="C39" s="16" t="n">
         <f aca="false">C35/253</f>
@@ -39665,10 +39820,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>2324</v>
+        <v>2331</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>2325</v>
+        <v>2332</v>
       </c>
       <c r="C40" s="16" t="n">
         <f aca="false">E35</f>
@@ -39677,10 +39832,10 @@
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>2326</v>
+        <v>2333</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>2327</v>
+        <v>2334</v>
       </c>
       <c r="C41" s="16" t="n">
         <f aca="false">SUM(D2:D7)/SUM(C2:C7)</f>
@@ -39689,25 +39844,25 @@
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>2328</v>
+        <v>2335</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>2329</v>
+        <v>2336</v>
       </c>
       <c r="C42" s="16" t="n">
-        <f aca="false">(COUNTIF(Katalog!$Q$2:$Q$310,"Havola tekshirilgan*")+COUNTIF(Katalog!$Q$2:$Q$310,"Metadata tekshirilgan*"))/COUNTA(Katalog!$A$2:$A$310)</f>
-        <v>0.990291262135922</v>
+        <f aca="false">(COUNTIF(Katalog!$Q$2:$Q$312,"Havola tekshirilgan*")+COUNTIF(Katalog!$Q$2:$Q$312,"Metadata tekshirilgan*"))/COUNTA(Katalog!$A$2:$A$312)</f>
+        <v>0.990353697749196</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>2330</v>
+        <v>2337</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>2331</v>
+        <v>2338</v>
       </c>
       <c r="C43" s="16" t="n">
-        <f aca="false">COUNT(Katalog!$X$2:$X$310)/COUNTA(Katalog!$A$2:$A$310)</f>
+        <f aca="false">COUNT(Katalog!$X$2:$X$312)/COUNTA(Katalog!$A$2:$A$312)</f>
         <v>0</v>
       </c>
     </row>
@@ -39739,400 +39894,400 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2332</v>
+        <v>2339</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2333</v>
+        <v>2340</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2334</v>
+        <v>2341</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>2335</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>2336</v>
+        <v>2343</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>2337</v>
+        <v>2344</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2338</v>
+        <v>2345</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>2339</v>
+        <v>2346</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>2340</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>2341</v>
+        <v>2348</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>2342</v>
+        <v>2349</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2343</v>
+        <v>2350</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>2344</v>
+        <v>2351</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>2345</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>2346</v>
+        <v>2353</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>2347</v>
+        <v>2354</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2348</v>
+        <v>2355</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2349</v>
+        <v>2356</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>2350</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>2351</v>
+        <v>2358</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2352</v>
+        <v>2359</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2353</v>
+        <v>2360</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>2349</v>
+        <v>2356</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>2354</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>2355</v>
+        <v>2362</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>2363</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>2364</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>2356</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>2357</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>2349</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>2358</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>2359</v>
+        <v>2366</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>2360</v>
+        <v>2367</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2361</v>
+        <v>2368</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>2349</v>
+        <v>2356</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>2362</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>2363</v>
+        <v>2370</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>2364</v>
+        <v>2371</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2365</v>
+        <v>2372</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>2366</v>
+        <v>2373</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>2367</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>2368</v>
+        <v>2375</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>2369</v>
+        <v>2376</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2370</v>
+        <v>2377</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>2371</v>
+        <v>2378</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>2372</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>2373</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>2374</v>
+        <v>2381</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>2375</v>
+        <v>2382</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>2194</v>
+        <v>2201</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>2376</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>2377</v>
+        <v>2384</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>2378</v>
+        <v>2385</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2379</v>
+        <v>2386</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>2380</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>2377</v>
+        <v>2384</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>2381</v>
+        <v>2388</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2382</v>
+        <v>2389</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2383</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>2377</v>
+        <v>2384</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>2384</v>
+        <v>2391</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2385</v>
+        <v>2392</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2386</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>2377</v>
+        <v>2384</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>2387</v>
+        <v>2394</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2388</v>
+        <v>2395</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2389</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>2377</v>
+        <v>2384</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>2390</v>
+        <v>2397</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2391</v>
+        <v>2398</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>2392</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>2377</v>
+        <v>2384</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>2393</v>
+        <v>2400</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2394</v>
+        <v>2401</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2395</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>2396</v>
+        <v>2403</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>95</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2397</v>
+        <v>2404</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2398</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>2399</v>
+        <v>2406</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2400</v>
+        <v>2407</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>2401</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>2399</v>
+        <v>2406</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2402</v>
+        <v>2409</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>2403</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>2399</v>
+        <v>2406</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>2404</v>
+        <v>2411</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2405</v>
+        <v>2412</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>2406</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>2399</v>
+        <v>2406</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>2407</v>
+        <v>2414</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2408</v>
+        <v>2415</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>2409</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>2315</v>
+        <v>2322</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2410</v>
+        <v>2417</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2411</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>2315</v>
+        <v>2322</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>201</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2412</v>
+        <v>2419</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>2413</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>2315</v>
+        <v>2322</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>354</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>2414</v>
+        <v>2421</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>2415</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>2416</v>
+        <v>2423</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>482</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>2417</v>
+        <v>2424</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>2418</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>2419</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>2420</v>
+        <v>2427</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>2421</v>
+        <v>2428</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>2422</v>
+        <v>2429</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>41</v>
@@ -40140,86 +40295,86 @@
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>2423</v>
+        <v>2430</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>2424</v>
+        <v>2431</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>2425</v>
+        <v>2432</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>2426</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>2427</v>
+        <v>2434</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>2428</v>
+        <v>2435</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>2429</v>
+        <v>2436</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>2426</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>2430</v>
+        <v>2437</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>2431</v>
+        <v>2438</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>2432</v>
+        <v>2439</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>2433</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>2434</v>
+        <v>2441</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>2435</v>
+        <v>2442</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>2436</v>
+        <v>2443</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>2437</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>2438</v>
+        <v>2445</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>2439</v>
+        <v>2446</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>2440</v>
+        <v>2447</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>2441</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>2442</v>
+        <v>2449</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>2443</v>
+        <v>2450</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>2444</v>
+        <v>2451</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>2445</v>
+        <v>2452</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
+++ b/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7133" uniqueCount="2453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7183" uniqueCount="2464">
   <si>
     <t xml:space="preserve">SHOKALON — videodarslar katalogi, 7-versiya</t>
   </si>
@@ -6632,6 +6632,39 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.youtube.com/watch?v=0fwT622SLB8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saphenous Vein Doppler Ultrasound Normal Vs Abnormal | Varicose Veins | Lower Limb Vascular USG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=-4tJgiWazjA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How To: Abdominal Ultrasound - Aorta Measurements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=SHhKyEaW1NM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonosite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ishlab chiqaruvchi (Sonosite)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vascular and Biliary Complications after Liver Transplantation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=4etSnUtYJ7k</t>
   </si>
   <si>
     <t xml:space="preserve">Qidiruvdagi ma’lumot</t>
@@ -9849,7 +9882,7 @@
       </c>
       <c r="E65" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A65,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A65&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
@@ -10555,7 +10588,7 @@
       </c>
       <c r="E93" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A93,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A93&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7" t="s">
@@ -12694,7 +12727,7 @@
       </c>
       <c r="E178" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A178,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A178&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F178" s="7"/>
       <c r="G178" s="7"/>
@@ -12719,7 +12752,7 @@
       </c>
       <c r="E179" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A179,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A179&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F179" s="7"/>
       <c r="G179" s="7"/>
@@ -12769,7 +12802,7 @@
       </c>
       <c r="E181" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A181,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A181&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F181" s="7"/>
       <c r="G181" s="7"/>
@@ -17406,7 +17439,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y312"/>
+  <dimension ref="A1:Y315"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -37468,7 +37501,7 @@
       </c>
       <c r="Y310" s="13"/>
     </row>
-    <row r="311" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="7" t="s">
         <v>2193</v>
       </c>
@@ -37533,7 +37566,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="7" t="s">
         <v>2197</v>
       </c>
@@ -37598,6 +37631,205 @@
       </c>
       <c r="Y312" s="13" t="s">
         <v>2196</v>
+      </c>
+    </row>
+    <row r="313" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="7" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B313" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="C313" s="7"/>
+      <c r="D313" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B313,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.6. Yuzaki venalar va varikoz.</v>
+      </c>
+      <c r="E313" s="7" t="s">
+        <v>2201</v>
+      </c>
+      <c r="F313" s="12" t="s">
+        <v>2202</v>
+      </c>
+      <c r="G313" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="H313" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="I313" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J313" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K313" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L313" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="M313" s="7" t="s">
+        <v>897</v>
+      </c>
+      <c r="N313" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O313" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P313" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q313" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R313" s="13"/>
+      <c r="S313" s="13"/>
+      <c r="T313" s="13"/>
+      <c r="U313" s="13"/>
+      <c r="V313" s="13"/>
+      <c r="W313" s="13"/>
+      <c r="X313" s="7" t="str">
+        <f aca="false">IF(COUNT(R313:W313)=6,SUM(R313:W313),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y313" s="13" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="314" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A314" s="7" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B314" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C314" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D314" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B314,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.7. Qorin aortasi va pastki kava vena.</v>
+      </c>
+      <c r="E314" s="7" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F314" s="12" t="s">
+        <v>2205</v>
+      </c>
+      <c r="G314" s="7" t="s">
+        <v>2206</v>
+      </c>
+      <c r="H314" s="7" t="s">
+        <v>2207</v>
+      </c>
+      <c r="I314" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J314" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K314" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L314" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="M314" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="N314" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O314" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P314" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q314" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R314" s="13"/>
+      <c r="S314" s="13"/>
+      <c r="T314" s="13"/>
+      <c r="U314" s="13"/>
+      <c r="V314" s="13"/>
+      <c r="W314" s="13"/>
+      <c r="X314" s="7" t="str">
+        <f aca="false">IF(COUNT(R314:W314)=6,SUM(R314:W314),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y314" s="13" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="315" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A315" s="7" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B315" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="C315" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D315" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B315,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.9. Transplantat tomirlari.</v>
+      </c>
+      <c r="E315" s="7" t="s">
+        <v>2209</v>
+      </c>
+      <c r="F315" s="12" t="s">
+        <v>2210</v>
+      </c>
+      <c r="G315" s="7" t="s">
+        <v>2148</v>
+      </c>
+      <c r="H315" s="7" t="s">
+        <v>2149</v>
+      </c>
+      <c r="I315" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J315" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K315" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L315" s="7" t="s">
+        <v>1683</v>
+      </c>
+      <c r="M315" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="N315" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O315" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P315" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q315" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R315" s="13"/>
+      <c r="S315" s="13"/>
+      <c r="T315" s="13"/>
+      <c r="U315" s="13"/>
+      <c r="V315" s="13"/>
+      <c r="W315" s="13"/>
+      <c r="X315" s="7" t="str">
+        <f aca="false">IF(COUNT(R315:W315)=6,SUM(R315:W315),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y315" s="13" t="s">
+        <v>2130</v>
       </c>
     </row>
   </sheetData>
@@ -37920,6 +38152,9 @@
     <hyperlink ref="F310" r:id="rId309" display="https://www.youtube.com/watch?v=9pqoVZEEyrg"/>
     <hyperlink ref="F311" r:id="rId310" display="https://www.youtube.com/watch?v=66KjiicFGL4"/>
     <hyperlink ref="F312" r:id="rId311" display="https://www.youtube.com/watch?v=0fwT622SLB8"/>
+    <hyperlink ref="F313" r:id="rId312" display="https://www.youtube.com/watch?v=-4tJgiWazjA"/>
+    <hyperlink ref="F314" r:id="rId313" display="https://www.youtube.com/watch?v=SHhKyEaW1NM"/>
+    <hyperlink ref="F315" r:id="rId314" display="https://www.youtube.com/watch?v=4etSnUtYJ7k"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -37928,7 +38163,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId312"/>
+  <drawing r:id="rId315"/>
 </worksheet>
 </file>
 
@@ -37950,195 +38185,195 @@
         <v>746</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2200</v>
+        <v>2211</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2201</v>
+        <v>2212</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>2202</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>2203</v>
+        <v>2214</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>2204</v>
+        <v>2215</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2205</v>
+        <v>2216</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>2207</v>
+        <v>2218</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>2208</v>
+        <v>2219</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2209</v>
+        <v>2220</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>2210</v>
+        <v>2221</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>2211</v>
+        <v>2222</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2212</v>
+        <v>2223</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>2213</v>
+        <v>2224</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2214</v>
+        <v>2225</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2215</v>
+        <v>2226</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>2216</v>
+        <v>2227</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>2217</v>
+        <v>2228</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2218</v>
+        <v>2229</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>2219</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>2220</v>
+        <v>2231</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>2221</v>
+        <v>2232</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2222</v>
+        <v>2233</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>2224</v>
+        <v>2235</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>2225</v>
+        <v>2236</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2226</v>
+        <v>2237</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>2227</v>
+        <v>2238</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>2228</v>
+        <v>2239</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2229</v>
+        <v>2240</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>2231</v>
+        <v>2242</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>2232</v>
+        <v>2243</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>2233</v>
+        <v>2244</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>2234</v>
+        <v>2245</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>2235</v>
+        <v>2246</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>2236</v>
+        <v>2247</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>2237</v>
+        <v>2248</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>2238</v>
+        <v>2249</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>2239</v>
+        <v>2250</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>2219</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>2240</v>
+        <v>2251</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>2241</v>
+        <v>2252</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2242</v>
+        <v>2253</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>2243</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>2244</v>
+        <v>2255</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>2245</v>
+        <v>2256</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2246</v>
+        <v>2257</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38149,10 +38384,10 @@
         <v>962</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2247</v>
+        <v>2258</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2248</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38163,10 +38398,10 @@
         <v>1054</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2247</v>
+        <v>2258</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2248</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38177,430 +38412,430 @@
         <v>1060</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2247</v>
+        <v>2258</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>2248</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>2249</v>
+        <v>2260</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>2250</v>
+        <v>2261</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2229</v>
+        <v>2240</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>2251</v>
+        <v>2262</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>2252</v>
+        <v>2263</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2233</v>
+        <v>2244</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>2253</v>
+        <v>2264</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>2254</v>
+        <v>2265</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2255</v>
+        <v>2266</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>2256</v>
+        <v>2267</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>2257</v>
+        <v>2268</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2258</v>
+        <v>2269</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>2259</v>
+        <v>2270</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>2260</v>
+        <v>2271</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2261</v>
+        <v>2272</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>2262</v>
+        <v>2273</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>2263</v>
+        <v>2274</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2261</v>
+        <v>2272</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>2264</v>
+        <v>2275</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>2265</v>
+        <v>2276</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2261</v>
+        <v>2272</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>2266</v>
+        <v>2277</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>2267</v>
+        <v>2278</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2268</v>
+        <v>2279</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>2269</v>
+        <v>2280</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>2270</v>
+        <v>2281</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>2271</v>
+        <v>2282</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>2272</v>
+        <v>2283</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>2273</v>
+        <v>2284</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>2274</v>
+        <v>2285</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>2275</v>
+        <v>2286</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>2276</v>
+        <v>2287</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>2277</v>
+        <v>2288</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>2278</v>
+        <v>2289</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>2279</v>
+        <v>2290</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>2280</v>
+        <v>2291</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>2281</v>
+        <v>2292</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>2282</v>
+        <v>2293</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>2268</v>
+        <v>2279</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>2283</v>
+        <v>2294</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>2284</v>
+        <v>2295</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>2261</v>
+        <v>2272</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>2285</v>
+        <v>2296</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>2286</v>
+        <v>2297</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>2261</v>
+        <v>2272</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>2287</v>
+        <v>2298</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>2288</v>
+        <v>2299</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>2268</v>
+        <v>2279</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>2289</v>
+        <v>2300</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>2290</v>
+        <v>2301</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>2261</v>
+        <v>2272</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>2291</v>
+        <v>2302</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>2292</v>
+        <v>2303</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>2268</v>
+        <v>2279</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>2293</v>
+        <v>2304</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>2294</v>
+        <v>2305</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>2268</v>
+        <v>2279</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>2295</v>
+        <v>2306</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>2296</v>
+        <v>2307</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>2268</v>
+        <v>2279</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>2297</v>
+        <v>2308</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>2298</v>
+        <v>2309</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>2271</v>
+        <v>2282</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>2299</v>
+        <v>2310</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>2300</v>
+        <v>2311</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>2301</v>
+        <v>2312</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>2302</v>
+        <v>2313</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>2303</v>
+        <v>2314</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>2304</v>
+        <v>2315</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>2305</v>
+        <v>2316</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>2306</v>
+        <v>2317</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>2261</v>
+        <v>2272</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>2230</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>2307</v>
+        <v>2318</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>2188</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>2308</v>
+        <v>2319</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>2309</v>
+        <v>2320</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>2310</v>
+        <v>2321</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>2308</v>
+        <v>2319</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>2311</v>
+        <v>2322</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>2312</v>
+        <v>2323</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>2308</v>
+        <v>2319</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>2313</v>
+        <v>2324</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>2314</v>
+        <v>2325</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>2308</v>
+        <v>2319</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>2315</v>
+        <v>2326</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>2316</v>
+        <v>2327</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>2308</v>
+        <v>2319</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>2317</v>
+        <v>2328</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>2318</v>
+        <v>2329</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>2308</v>
+        <v>2319</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>2223</v>
+        <v>2234</v>
       </c>
     </row>
   </sheetData>
@@ -38686,22 +38921,22 @@
         <v>36</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2319</v>
+        <v>2330</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>2320</v>
+        <v>2331</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>2321</v>
+        <v>2332</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>2322</v>
+        <v>2333</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>2323</v>
+        <v>2334</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>2243</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39763,7 +39998,7 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="17"/>
       <c r="B35" s="17" t="s">
-        <v>2324</v>
+        <v>2335</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">SUM(C2:C34)</f>
@@ -39792,26 +40027,26 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>2325</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>2326</v>
+        <v>2337</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>2327</v>
+        <v>2338</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>2328</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>2329</v>
+        <v>2340</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>2330</v>
+        <v>2341</v>
       </c>
       <c r="C39" s="16" t="n">
         <f aca="false">C35/253</f>
@@ -39820,10 +40055,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>2331</v>
+        <v>2342</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>2332</v>
+        <v>2343</v>
       </c>
       <c r="C40" s="16" t="n">
         <f aca="false">E35</f>
@@ -39832,10 +40067,10 @@
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>2333</v>
+        <v>2344</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>2334</v>
+        <v>2345</v>
       </c>
       <c r="C41" s="16" t="n">
         <f aca="false">SUM(D2:D7)/SUM(C2:C7)</f>
@@ -39844,10 +40079,10 @@
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>2335</v>
+        <v>2346</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>2336</v>
+        <v>2347</v>
       </c>
       <c r="C42" s="16" t="n">
         <f aca="false">(COUNTIF(Katalog!$Q$2:$Q$312,"Havola tekshirilgan*")+COUNTIF(Katalog!$Q$2:$Q$312,"Metadata tekshirilgan*"))/COUNTA(Katalog!$A$2:$A$312)</f>
@@ -39856,10 +40091,10 @@
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>2337</v>
+        <v>2348</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>2338</v>
+        <v>2349</v>
       </c>
       <c r="C43" s="16" t="n">
         <f aca="false">COUNT(Katalog!$X$2:$X$312)/COUNTA(Katalog!$A$2:$A$312)</f>
@@ -39894,400 +40129,400 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2339</v>
+        <v>2350</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2340</v>
+        <v>2351</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2341</v>
+        <v>2352</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>2342</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>2343</v>
+        <v>2354</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>2344</v>
+        <v>2355</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2345</v>
+        <v>2356</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>2346</v>
+        <v>2357</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>2347</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>2348</v>
+        <v>2359</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>2349</v>
+        <v>2360</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2350</v>
+        <v>2361</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>2351</v>
+        <v>2362</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>2352</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>2353</v>
+        <v>2364</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>2354</v>
+        <v>2365</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2355</v>
+        <v>2366</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2356</v>
+        <v>2367</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>2357</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>2358</v>
+        <v>2369</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2359</v>
+        <v>2370</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2360</v>
+        <v>2371</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>2356</v>
+        <v>2367</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>2361</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>2362</v>
+        <v>2373</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>2363</v>
+        <v>2374</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2364</v>
+        <v>2375</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>2356</v>
+        <v>2367</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>2365</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>2366</v>
+        <v>2377</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>2378</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>2379</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>2367</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>2368</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>2356</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>2369</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>2370</v>
+        <v>2381</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>2371</v>
+        <v>2382</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2372</v>
+        <v>2383</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>2373</v>
+        <v>2384</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>2374</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>2375</v>
+        <v>2386</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>2376</v>
+        <v>2387</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2377</v>
+        <v>2388</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>2378</v>
+        <v>2389</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>2379</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>2380</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>2381</v>
+        <v>2392</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>2382</v>
+        <v>2393</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>2201</v>
+        <v>2212</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>2383</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>2384</v>
+        <v>2395</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>2385</v>
+        <v>2396</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2386</v>
+        <v>2397</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>2387</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>2384</v>
+        <v>2395</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>2388</v>
+        <v>2399</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2389</v>
+        <v>2400</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2390</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>2384</v>
+        <v>2395</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>2391</v>
+        <v>2402</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2392</v>
+        <v>2403</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2393</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>2384</v>
+        <v>2395</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>2394</v>
+        <v>2405</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2395</v>
+        <v>2406</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2396</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>2384</v>
+        <v>2395</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>2397</v>
+        <v>2408</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2398</v>
+        <v>2409</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>2399</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>2384</v>
+        <v>2395</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>2400</v>
+        <v>2411</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2401</v>
+        <v>2412</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2402</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>2403</v>
+        <v>2414</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>95</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2404</v>
+        <v>2415</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2405</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>2406</v>
+        <v>2417</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2407</v>
+        <v>2418</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>2408</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>2406</v>
+        <v>2417</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2409</v>
+        <v>2420</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>2410</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>2406</v>
+        <v>2417</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>2411</v>
+        <v>2422</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2412</v>
+        <v>2423</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>2413</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>2406</v>
+        <v>2417</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>2414</v>
+        <v>2425</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2415</v>
+        <v>2426</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>2416</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>2322</v>
+        <v>2333</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2417</v>
+        <v>2428</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2418</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>2322</v>
+        <v>2333</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>201</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2419</v>
+        <v>2430</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>2420</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>2322</v>
+        <v>2333</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>354</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>2421</v>
+        <v>2432</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>2422</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>2423</v>
+        <v>2434</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>482</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>2424</v>
+        <v>2435</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>2425</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>2426</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>2427</v>
+        <v>2438</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>2428</v>
+        <v>2439</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>2429</v>
+        <v>2440</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>41</v>
@@ -40295,86 +40530,86 @@
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>2430</v>
+        <v>2441</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>2431</v>
+        <v>2442</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>2432</v>
+        <v>2443</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>2433</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>2434</v>
+        <v>2445</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>2435</v>
+        <v>2446</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>2436</v>
+        <v>2447</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>2433</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>2437</v>
+        <v>2448</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>2438</v>
+        <v>2449</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>2439</v>
+        <v>2450</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>2440</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>2441</v>
+        <v>2452</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>2442</v>
+        <v>2453</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>2443</v>
+        <v>2454</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>2444</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>2445</v>
+        <v>2456</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>2446</v>
+        <v>2457</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>2447</v>
+        <v>2458</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>2448</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>2449</v>
+        <v>2460</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>2450</v>
+        <v>2461</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>2451</v>
+        <v>2462</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>2452</v>
+        <v>2463</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
+++ b/docs/shokalon/02_VIDEO_CATALOG/SHOKALON_katalog_v7.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Audit" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Katalog!$A$1:$Y$312</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Katalog!$A$1:$Y$318</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Mundarija!$A$1:$I$254</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Qidiruv navbati'!$A$1:$F$117</definedName>
   </definedNames>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7183" uniqueCount="2464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7228" uniqueCount="2474">
   <si>
     <t xml:space="preserve">SHOKALON — videodarslar katalogi, 7-versiya</t>
   </si>
@@ -6665,6 +6665,36 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.youtube.com/watch?v=4etSnUtYJ7k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hot Tip-How to Locate the Vertebral Artery and Demonstrate Flow Direction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=0jwR7ClJZgo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imaging of Arteriovenous Fistulas: From Maturation to Salvage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=PeTOlKIaNBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeffrey Chen by SmartRad AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measuring dialysis fistula maturity using ultrasound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=ts4a50k08bE</t>
   </si>
   <si>
     <t xml:space="preserve">Qidiruvdagi ma’lumot</t>
@@ -12627,7 +12657,7 @@
       </c>
       <c r="E174" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A174,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A174&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F174" s="7"/>
       <c r="G174" s="7"/>
@@ -12777,7 +12807,7 @@
       </c>
       <c r="E180" s="7" t="n">
         <f aca="false">COUNTIFS(Katalog!$B:$B,A180,Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")+COUNTIFS(Katalog!$C:$C,"*"&amp;A180&amp;"*",Katalog!$Q:$Q,"&lt;&gt;Ishlamaydi*")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F180" s="7"/>
       <c r="G180" s="7"/>
@@ -17439,7 +17469,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y315"/>
+  <dimension ref="A1:Y318"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -37633,7 +37663,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="7" t="s">
         <v>2200</v>
       </c>
@@ -37698,7 +37728,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="7" t="s">
         <v>2203</v>
       </c>
@@ -37765,7 +37795,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="7" t="s">
         <v>2208</v>
       </c>
@@ -37832,8 +37862,197 @@
         <v>2130</v>
       </c>
     </row>
+    <row r="316" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A316" s="7" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B316" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C316" s="7"/>
+      <c r="D316" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B316,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.2. Karotid va vertebral arteriyalar.</v>
+      </c>
+      <c r="E316" s="7" t="s">
+        <v>2212</v>
+      </c>
+      <c r="F316" s="12" t="s">
+        <v>2213</v>
+      </c>
+      <c r="G316" s="7" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H316" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="I316" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J316" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K316" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L316" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="M316" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="N316" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O316" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P316" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q316" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R316" s="13"/>
+      <c r="S316" s="13"/>
+      <c r="T316" s="13"/>
+      <c r="U316" s="13"/>
+      <c r="V316" s="13"/>
+      <c r="W316" s="13"/>
+      <c r="X316" s="7" t="str">
+        <f aca="false">IF(COUNT(R316:W316)=6,SUM(R316:W316),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y316" s="13"/>
+    </row>
+    <row r="317" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A317" s="7" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B317" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="C317" s="7"/>
+      <c r="D317" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B317,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.8. Gemodializ arteriovenoz kirish yo‘llari.</v>
+      </c>
+      <c r="E317" s="7" t="s">
+        <v>2215</v>
+      </c>
+      <c r="F317" s="12" t="s">
+        <v>2216</v>
+      </c>
+      <c r="G317" s="7" t="s">
+        <v>2217</v>
+      </c>
+      <c r="H317" s="7" t="s">
+        <v>1714</v>
+      </c>
+      <c r="I317" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J317" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K317" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L317" s="7" t="s">
+        <v>1683</v>
+      </c>
+      <c r="M317" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="N317" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O317" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P317" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q317" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R317" s="13"/>
+      <c r="S317" s="13"/>
+      <c r="T317" s="13"/>
+      <c r="U317" s="13"/>
+      <c r="V317" s="13"/>
+      <c r="W317" s="13"/>
+      <c r="X317" s="7" t="str">
+        <f aca="false">IF(COUNT(R317:W317)=6,SUM(R317:W317),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y317" s="13"/>
+    </row>
+    <row r="318" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="7" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B318" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="C318" s="7"/>
+      <c r="D318" s="7" t="str">
+        <f aca="false">IFERROR(INDEX(Mundarija!$D:$D,MATCH(B318,Mundarija!$A:$A,0)),"kod topilmadi")</f>
+        <v>25.8. Gemodializ arteriovenoz kirish yo‘llari.</v>
+      </c>
+      <c r="E318" s="7" t="s">
+        <v>2219</v>
+      </c>
+      <c r="F318" s="12" t="s">
+        <v>2220</v>
+      </c>
+      <c r="G318" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H318" s="7" t="s">
+        <v>1777</v>
+      </c>
+      <c r="I318" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="J318" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="K318" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="L318" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="M318" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="N318" s="13" t="s">
+        <v>816</v>
+      </c>
+      <c r="O318" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="P318" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q318" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R318" s="13"/>
+      <c r="S318" s="13"/>
+      <c r="T318" s="13"/>
+      <c r="U318" s="13"/>
+      <c r="V318" s="13"/>
+      <c r="W318" s="13"/>
+      <c r="X318" s="7" t="str">
+        <f aca="false">IF(COUNT(R318:W318)=6,SUM(R318:W318),"ko‘rilmagan")</f>
+        <v>ko‘rilmagan</v>
+      </c>
+      <c r="Y318" s="13"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y312"/>
+  <autoFilter ref="A1:Y318"/>
   <dataValidations count="1">
     <dataValidation allowBlank="true" error="0 dan 5 gacha butun son" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="R2:W492" type="whole">
       <formula1>0</formula1>
@@ -38155,6 +38374,9 @@
     <hyperlink ref="F313" r:id="rId312" display="https://www.youtube.com/watch?v=-4tJgiWazjA"/>
     <hyperlink ref="F314" r:id="rId313" display="https://www.youtube.com/watch?v=SHhKyEaW1NM"/>
     <hyperlink ref="F315" r:id="rId314" display="https://www.youtube.com/watch?v=4etSnUtYJ7k"/>
+    <hyperlink ref="F316" r:id="rId315" display="https://www.youtube.com/watch?v=0jwR7ClJZgo"/>
+    <hyperlink ref="F317" r:id="rId316" display="https://www.youtube.com/watch?v=PeTOlKIaNBI"/>
+    <hyperlink ref="F318" r:id="rId317" display="https://www.youtube.com/watch?v=ts4a50k08bE"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -38163,7 +38385,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId315"/>
+  <drawing r:id="rId318"/>
 </worksheet>
 </file>
 
@@ -38185,195 +38407,195 @@
         <v>746</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2211</v>
+        <v>2221</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2212</v>
+        <v>2222</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>2213</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>2214</v>
+        <v>2224</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>2215</v>
+        <v>2225</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2216</v>
+        <v>2226</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>2217</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>2218</v>
+        <v>2228</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>2219</v>
+        <v>2229</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2220</v>
+        <v>2230</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>2217</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>2221</v>
+        <v>2231</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>2222</v>
+        <v>2232</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2223</v>
+        <v>2233</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2217</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>2224</v>
+        <v>2234</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2225</v>
+        <v>2235</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2226</v>
+        <v>2236</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>2217</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>2227</v>
+        <v>2237</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>2228</v>
+        <v>2238</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2229</v>
+        <v>2239</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>2230</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>2231</v>
+        <v>2241</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>2232</v>
+        <v>2242</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2233</v>
+        <v>2243</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>2235</v>
+        <v>2245</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>2236</v>
+        <v>2246</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2237</v>
+        <v>2247</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>2238</v>
+        <v>2248</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>2239</v>
+        <v>2249</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2240</v>
+        <v>2250</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>2242</v>
+        <v>2252</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>2243</v>
+        <v>2253</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>2244</v>
+        <v>2254</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>2245</v>
+        <v>2255</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>2246</v>
+        <v>2256</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>2247</v>
+        <v>2257</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>2248</v>
+        <v>2258</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>2249</v>
+        <v>2259</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>2250</v>
+        <v>2260</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>2230</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>2251</v>
+        <v>2261</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>2252</v>
+        <v>2262</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2253</v>
+        <v>2263</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>2254</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>2255</v>
+        <v>2265</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>2256</v>
+        <v>2266</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2257</v>
+        <v>2267</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38384,10 +38606,10 @@
         <v>962</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2258</v>
+        <v>2268</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2259</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38398,10 +38620,10 @@
         <v>1054</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2258</v>
+        <v>2268</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2259</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38412,430 +38634,430 @@
         <v>1060</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2258</v>
+        <v>2268</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>2259</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>2260</v>
+        <v>2270</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>2261</v>
+        <v>2271</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2240</v>
+        <v>2250</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>2262</v>
+        <v>2272</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>2263</v>
+        <v>2273</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2244</v>
+        <v>2254</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>2264</v>
+        <v>2274</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>2265</v>
+        <v>2275</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2266</v>
+        <v>2276</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>2267</v>
+        <v>2277</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>2268</v>
+        <v>2278</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2269</v>
+        <v>2279</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>2270</v>
+        <v>2280</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>2271</v>
+        <v>2281</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2272</v>
+        <v>2282</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>2273</v>
+        <v>2283</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>2274</v>
+        <v>2284</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2272</v>
+        <v>2282</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>2275</v>
+        <v>2285</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>2276</v>
+        <v>2286</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2272</v>
+        <v>2282</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>2277</v>
+        <v>2287</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>2278</v>
+        <v>2288</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2279</v>
+        <v>2289</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>2280</v>
+        <v>2290</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>2281</v>
+        <v>2291</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>2282</v>
+        <v>2292</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>2283</v>
+        <v>2293</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>2284</v>
+        <v>2294</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>2285</v>
+        <v>2295</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>2286</v>
+        <v>2296</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>2287</v>
+        <v>2297</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>2288</v>
+        <v>2298</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>2289</v>
+        <v>2299</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>2290</v>
+        <v>2300</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>2291</v>
+        <v>2301</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>2293</v>
+        <v>2303</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>2279</v>
+        <v>2289</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>2294</v>
+        <v>2304</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>2295</v>
+        <v>2305</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>2272</v>
+        <v>2282</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>2296</v>
+        <v>2306</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>2297</v>
+        <v>2307</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>2272</v>
+        <v>2282</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>2298</v>
+        <v>2308</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>2299</v>
+        <v>2309</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>2279</v>
+        <v>2289</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>2300</v>
+        <v>2310</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>2301</v>
+        <v>2311</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>2272</v>
+        <v>2282</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>2302</v>
+        <v>2312</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>2303</v>
+        <v>2313</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>2279</v>
+        <v>2289</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>2304</v>
+        <v>2314</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>2305</v>
+        <v>2315</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>2279</v>
+        <v>2289</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>2306</v>
+        <v>2316</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>2307</v>
+        <v>2317</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>2279</v>
+        <v>2289</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>2308</v>
+        <v>2318</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>2309</v>
+        <v>2319</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>2282</v>
+        <v>2292</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>2310</v>
+        <v>2320</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>2311</v>
+        <v>2321</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>2312</v>
+        <v>2322</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>2313</v>
+        <v>2323</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>2314</v>
+        <v>2324</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>2315</v>
+        <v>2325</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>2316</v>
+        <v>2326</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>2317</v>
+        <v>2327</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>2272</v>
+        <v>2282</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>2241</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>2318</v>
+        <v>2328</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>2188</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>2320</v>
+        <v>2330</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>2321</v>
+        <v>2331</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>2322</v>
+        <v>2332</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>2323</v>
+        <v>2333</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>2324</v>
+        <v>2334</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>2325</v>
+        <v>2335</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>2326</v>
+        <v>2336</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>2327</v>
+        <v>2337</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>2328</v>
+        <v>2338</v>
       </c>
       <c r="B47" s="7" t="s">
+        <v>2339</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>2329</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>2319</v>
-      </c>
       <c r="D47" s="7" t="s">
-        <v>2234</v>
+        <v>2244</v>
       </c>
     </row>
   </sheetData>
@@ -38921,22 +39143,22 @@
         <v>36</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2330</v>
+        <v>2340</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>2331</v>
+        <v>2341</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>2332</v>
+        <v>2342</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>2333</v>
+        <v>2343</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>2334</v>
+        <v>2344</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>2254</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39998,7 +40220,7 @@
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="17"/>
       <c r="B35" s="17" t="s">
-        <v>2335</v>
+        <v>2345</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">SUM(C2:C34)</f>
@@ -40027,26 +40249,26 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>2336</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>2337</v>
+        <v>2347</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>2338</v>
+        <v>2348</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>2339</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>2340</v>
+        <v>2350</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>2341</v>
+        <v>2351</v>
       </c>
       <c r="C39" s="16" t="n">
         <f aca="false">C35/253</f>
@@ -40055,10 +40277,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>2342</v>
+        <v>2352</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>2343</v>
+        <v>2353</v>
       </c>
       <c r="C40" s="16" t="n">
         <f aca="false">E35</f>
@@ -40067,10 +40289,10 @@
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>2344</v>
+        <v>2354</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>2345</v>
+        <v>2355</v>
       </c>
       <c r="C41" s="16" t="n">
         <f aca="false">SUM(D2:D7)/SUM(C2:C7)</f>
@@ -40079,10 +40301,10 @@
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>2346</v>
+        <v>2356</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>2347</v>
+        <v>2357</v>
       </c>
       <c r="C42" s="16" t="n">
         <f aca="false">(COUNTIF(Katalog!$Q$2:$Q$312,"Havola tekshirilgan*")+COUNTIF(Katalog!$Q$2:$Q$312,"Metadata tekshirilgan*"))/COUNTA(Katalog!$A$2:$A$312)</f>
@@ -40091,10 +40313,10 @@
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>2348</v>
+        <v>2358</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>2349</v>
+        <v>2359</v>
       </c>
       <c r="C43" s="16" t="n">
         <f aca="false">COUNT(Katalog!$X$2:$X$312)/COUNTA(Katalog!$A$2:$A$312)</f>
@@ -40129,400 +40351,400 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2350</v>
+        <v>2360</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2351</v>
+        <v>2361</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>2352</v>
+        <v>2362</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>2353</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>2354</v>
+        <v>2364</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>2355</v>
+        <v>2365</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2356</v>
+        <v>2366</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>2357</v>
+        <v>2367</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>2358</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>2359</v>
+        <v>2369</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>2360</v>
+        <v>2370</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2361</v>
+        <v>2371</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>2362</v>
+        <v>2372</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>2363</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>2364</v>
+        <v>2374</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>2365</v>
+        <v>2375</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2366</v>
+        <v>2376</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>2367</v>
+        <v>2377</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>2368</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>2369</v>
+        <v>2379</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2370</v>
+        <v>2380</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2371</v>
+        <v>2381</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>2367</v>
+        <v>2377</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>2372</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>2373</v>
+        <v>2383</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>2374</v>
+        <v>2384</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2375</v>
+        <v>2385</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>2367</v>
+        <v>2377</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>2376</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>2377</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>2378</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>2379</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>2367</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>2380</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>2381</v>
+        <v>2391</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>2382</v>
+        <v>2392</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2383</v>
+        <v>2393</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>2384</v>
+        <v>2394</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>2385</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>2386</v>
+        <v>2396</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>2387</v>
+        <v>2397</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2388</v>
+        <v>2398</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>2389</v>
+        <v>2399</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>2390</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>2391</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>2392</v>
+        <v>2402</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>2393</v>
+        <v>2403</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>2212</v>
+        <v>2222</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>2394</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>2395</v>
+        <v>2405</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>2396</v>
+        <v>2406</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2397</v>
+        <v>2407</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>2398</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>2395</v>
+        <v>2405</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>2399</v>
+        <v>2409</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2400</v>
+        <v>2410</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>2401</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>2395</v>
+        <v>2405</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>2402</v>
+        <v>2412</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2403</v>
+        <v>2413</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>2404</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>2395</v>
+        <v>2405</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>2405</v>
+        <v>2415</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2406</v>
+        <v>2416</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>2407</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>2395</v>
+        <v>2405</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>2408</v>
+        <v>2418</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2409</v>
+        <v>2419</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>2410</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>2395</v>
+        <v>2405</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>2411</v>
+        <v>2421</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2412</v>
+        <v>2422</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>2413</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>2414</v>
+        <v>2424</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>95</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2415</v>
+        <v>2425</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>2416</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>2417</v>
+        <v>2427</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2418</v>
+        <v>2428</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>2419</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>2417</v>
+        <v>2427</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2420</v>
+        <v>2430</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>2421</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>2417</v>
+        <v>2427</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>2422</v>
+        <v>2432</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2423</v>
+        <v>2433</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>2424</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>2417</v>
+        <v>2427</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>2425</v>
+        <v>2435</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2426</v>
+        <v>2436</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>2427</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>2333</v>
+        <v>2343</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>185</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2428</v>
+        <v>2438</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>2429</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>2333</v>
+        <v>2343</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>201</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2430</v>
+        <v>2440</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>2431</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>2333</v>
+        <v>2343</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>354</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>2432</v>
+        <v>2442</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>2433</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>2434</v>
+        <v>2444</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>482</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>2435</v>
+        <v>2445</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>2436</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>2437</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>2438</v>
+        <v>2448</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>2439</v>
+        <v>2449</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>2440</v>
+        <v>2450</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>41</v>
@@ -40530,86 +40752,86 @@
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>2441</v>
+        <v>2451</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>2442</v>
+        <v>2452</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>2443</v>
+        <v>2453</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>2444</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>2445</v>
+        <v>2455</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>2446</v>
+        <v>2456</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>2447</v>
+        <v>2457</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>2444</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>2448</v>
+        <v>2458</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>2449</v>
+        <v>2459</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>2450</v>
+        <v>2460</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>2451</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>2452</v>
+        <v>2462</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>2453</v>
+        <v>2463</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>2454</v>
+        <v>2464</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>2455</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>2456</v>
+        <v>2466</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>2457</v>
+        <v>2467</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>2458</v>
+        <v>2468</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>2459</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>2460</v>
+        <v>2470</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>2461</v>
+        <v>2471</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>2462</v>
+        <v>2472</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>2463</v>
+        <v>2473</v>
       </c>
     </row>
   </sheetData>
